--- a/Overpotnital/O2/30K/Edited/CN Polyol O2_edited.xlsx
+++ b/Overpotnital/O2/30K/Edited/CN Polyol O2_edited.xlsx
@@ -649,7 +649,7 @@
       <c r="D4" s="0" t="n">
         <v>0.0196</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4" s="0" t="n">
         <v>0.014</v>
       </c>
       <c r="F4" s="0">
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="S4" s="0" t="n">
-        <v>-0.48223</v>
+        <v>-0.509</v>
       </c>
       <c r="V4" s="0" t="n">
         <v>-6</v>
@@ -739,7 +739,7 @@
       <c r="D5" s="0" t="n">
         <v>0.0196</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5" s="0" t="n">
         <v>0.014</v>
       </c>
       <c r="F5" s="0">
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="S5" s="0" t="n">
-        <v>-0.04564</v>
+        <v>-0.0494</v>
       </c>
       <c r="V5" s="0" t="n">
         <v>-5.9</v>
@@ -821,7 +821,7 @@
       <c r="D6" s="0" t="n">
         <v>0.0196</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6" s="0" t="n">
         <v>0.014</v>
       </c>
       <c r="F6" s="0">
@@ -900,7 +900,7 @@
       <c r="D7" s="0" t="n">
         <v>0.0196</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7" s="0" t="n">
         <v>0.014</v>
       </c>
       <c r="F7" s="0">
@@ -983,7 +983,7 @@
       <c r="D8" s="0" t="n">
         <v>0.0196</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8" s="0" t="n">
         <v>0.014</v>
       </c>
       <c r="F8" s="0">
@@ -1057,7 +1057,7 @@
       <c r="D9" s="0" t="n">
         <v>0.0196</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9" s="0" t="n">
         <v>0.014</v>
       </c>
       <c r="F9" s="0">
@@ -1139,7 +1139,7 @@
       <c r="D10" s="0" t="n">
         <v>0.0196</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10" s="0" t="n">
         <v>0.014</v>
       </c>
       <c r="F10" s="0">
@@ -1213,7 +1213,7 @@
       <c r="D11" s="0" t="n">
         <v>0.0196</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E11" s="0" t="n">
         <v>0.014</v>
       </c>
       <c r="F11" s="0">
@@ -1296,7 +1296,7 @@
       <c r="D12" s="0" t="n">
         <v>0.0196</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E12" s="0" t="n">
         <v>0.014</v>
       </c>
       <c r="F12" s="0">
@@ -1374,7 +1374,7 @@
       <c r="D13" s="0" t="n">
         <v>0.0196</v>
       </c>
-      <c r="E13" t="n">
+      <c r="E13" s="0" t="n">
         <v>0.014</v>
       </c>
       <c r="F13" s="0">
@@ -1448,7 +1448,7 @@
       <c r="D14" s="0" t="n">
         <v>0.0196</v>
       </c>
-      <c r="E14" t="n">
+      <c r="E14" s="0" t="n">
         <v>0.014</v>
       </c>
       <c r="F14" s="0">
@@ -1522,7 +1522,7 @@
       <c r="D15" s="0" t="n">
         <v>0.0196</v>
       </c>
-      <c r="E15" t="n">
+      <c r="E15" s="0" t="n">
         <v>0.014</v>
       </c>
       <c r="F15" s="0">
@@ -1596,7 +1596,7 @@
       <c r="D16" s="0" t="n">
         <v>0.0196</v>
       </c>
-      <c r="E16" t="n">
+      <c r="E16" s="0" t="n">
         <v>0.014</v>
       </c>
       <c r="F16" s="0">
@@ -1670,7 +1670,7 @@
       <c r="D17" s="0" t="n">
         <v>0.0196</v>
       </c>
-      <c r="E17" t="n">
+      <c r="E17" s="0" t="n">
         <v>0.014</v>
       </c>
       <c r="F17" s="0">
@@ -1744,7 +1744,7 @@
       <c r="D18" s="0" t="n">
         <v>0.0196</v>
       </c>
-      <c r="E18" t="n">
+      <c r="E18" s="0" t="n">
         <v>0.014</v>
       </c>
       <c r="F18" s="0">
@@ -1818,7 +1818,7 @@
       <c r="D19" s="0" t="n">
         <v>0.0196</v>
       </c>
-      <c r="E19" t="n">
+      <c r="E19" s="0" t="n">
         <v>0.014</v>
       </c>
       <c r="F19" s="0">
@@ -1892,7 +1892,7 @@
       <c r="D20" s="0" t="n">
         <v>0.0196</v>
       </c>
-      <c r="E20" t="n">
+      <c r="E20" s="0" t="n">
         <v>0.014</v>
       </c>
       <c r="F20" s="0">
@@ -1966,7 +1966,7 @@
       <c r="D21" s="0" t="n">
         <v>0.0196</v>
       </c>
-      <c r="E21" t="n">
+      <c r="E21" s="0" t="n">
         <v>0.014</v>
       </c>
       <c r="F21" s="0">
@@ -2040,7 +2040,7 @@
       <c r="D22" s="0" t="n">
         <v>0.0196</v>
       </c>
-      <c r="E22" t="n">
+      <c r="E22" s="0" t="n">
         <v>0.014</v>
       </c>
       <c r="F22" s="0">
@@ -2114,7 +2114,7 @@
       <c r="D23" s="0" t="n">
         <v>0.0196</v>
       </c>
-      <c r="E23" t="n">
+      <c r="E23" s="0" t="n">
         <v>0.014</v>
       </c>
       <c r="F23" s="0">
@@ -2188,7 +2188,7 @@
       <c r="D24" s="0" t="n">
         <v>0.0196</v>
       </c>
-      <c r="E24" t="n">
+      <c r="E24" s="0" t="n">
         <v>0.014</v>
       </c>
       <c r="F24" s="0">
@@ -2262,7 +2262,7 @@
       <c r="D25" s="0" t="n">
         <v>0.0196</v>
       </c>
-      <c r="E25" t="n">
+      <c r="E25" s="0" t="n">
         <v>0.014</v>
       </c>
       <c r="F25" s="0">
@@ -2336,7 +2336,7 @@
       <c r="D26" s="0" t="n">
         <v>0.0196</v>
       </c>
-      <c r="E26" t="n">
+      <c r="E26" s="0" t="n">
         <v>0.014</v>
       </c>
       <c r="F26" s="0">
@@ -2410,7 +2410,7 @@
       <c r="D27" s="0" t="n">
         <v>0.0196</v>
       </c>
-      <c r="E27" t="n">
+      <c r="E27" s="0" t="n">
         <v>0.014</v>
       </c>
       <c r="F27" s="0">
@@ -2484,7 +2484,7 @@
       <c r="D28" s="0" t="n">
         <v>0.0196</v>
       </c>
-      <c r="E28" t="n">
+      <c r="E28" s="0" t="n">
         <v>0.014</v>
       </c>
       <c r="F28" s="0">
@@ -2558,7 +2558,7 @@
       <c r="D29" s="0" t="n">
         <v>0.0196</v>
       </c>
-      <c r="E29" t="n">
+      <c r="E29" s="0" t="n">
         <v>0.014</v>
       </c>
       <c r="F29" s="0">
@@ -2632,7 +2632,7 @@
       <c r="D30" s="0" t="n">
         <v>0.0196</v>
       </c>
-      <c r="E30" t="n">
+      <c r="E30" s="0" t="n">
         <v>0.014</v>
       </c>
       <c r="F30" s="0">
@@ -2706,7 +2706,7 @@
       <c r="D31" s="0" t="n">
         <v>0.0196</v>
       </c>
-      <c r="E31" t="n">
+      <c r="E31" s="0" t="n">
         <v>0.014</v>
       </c>
       <c r="F31" s="0">
@@ -2780,7 +2780,7 @@
       <c r="D32" s="0" t="n">
         <v>0.0196</v>
       </c>
-      <c r="E32" t="n">
+      <c r="E32" s="0" t="n">
         <v>0.014</v>
       </c>
       <c r="F32" s="0">
@@ -2847,7 +2847,7 @@
       <c r="D33" s="0" t="n">
         <v>0.0196</v>
       </c>
-      <c r="E33" t="n">
+      <c r="E33" s="0" t="n">
         <v>0.014</v>
       </c>
       <c r="F33" s="0">
@@ -2914,7 +2914,7 @@
       <c r="D34" s="0" t="n">
         <v>0.0196</v>
       </c>
-      <c r="E34" t="n">
+      <c r="E34" s="0" t="n">
         <v>0.014</v>
       </c>
       <c r="F34" s="0">
@@ -2981,7 +2981,7 @@
       <c r="D35" s="0" t="n">
         <v>0.0196</v>
       </c>
-      <c r="E35" t="n">
+      <c r="E35" s="0" t="n">
         <v>0.014</v>
       </c>
       <c r="F35" s="0">
@@ -3048,7 +3048,7 @@
       <c r="D36" s="0" t="n">
         <v>0.0196</v>
       </c>
-      <c r="E36" t="n">
+      <c r="E36" s="0" t="n">
         <v>0.014</v>
       </c>
       <c r="F36" s="0">
@@ -3115,7 +3115,7 @@
       <c r="D37" s="0" t="n">
         <v>0.0196</v>
       </c>
-      <c r="E37" t="n">
+      <c r="E37" s="0" t="n">
         <v>0.014</v>
       </c>
       <c r="F37" s="0">
@@ -3182,7 +3182,7 @@
       <c r="D38" s="0" t="n">
         <v>0.0196</v>
       </c>
-      <c r="E38" t="n">
+      <c r="E38" s="0" t="n">
         <v>0.014</v>
       </c>
       <c r="F38" s="0">
@@ -3249,7 +3249,7 @@
       <c r="D39" s="0" t="n">
         <v>0.0196</v>
       </c>
-      <c r="E39" t="n">
+      <c r="E39" s="0" t="n">
         <v>0.014</v>
       </c>
       <c r="F39" s="0">
@@ -3316,7 +3316,7 @@
       <c r="D40" s="0" t="n">
         <v>0.0196</v>
       </c>
-      <c r="E40" t="n">
+      <c r="E40" s="0" t="n">
         <v>0.014</v>
       </c>
       <c r="F40" s="0">
@@ -3383,7 +3383,7 @@
       <c r="D41" s="0" t="n">
         <v>0.0196</v>
       </c>
-      <c r="E41" t="n">
+      <c r="E41" s="0" t="n">
         <v>0.014</v>
       </c>
       <c r="F41" s="0">
@@ -3450,7 +3450,7 @@
       <c r="D42" s="0" t="n">
         <v>0.0196</v>
       </c>
-      <c r="E42" t="n">
+      <c r="E42" s="0" t="n">
         <v>0.014</v>
       </c>
       <c r="F42" s="0">
@@ -3517,7 +3517,7 @@
       <c r="D43" s="0" t="n">
         <v>0.0196</v>
       </c>
-      <c r="E43" t="n">
+      <c r="E43" s="0" t="n">
         <v>0.014</v>
       </c>
       <c r="F43" s="0">
@@ -3584,7 +3584,7 @@
       <c r="D44" s="0" t="n">
         <v>0.0196</v>
       </c>
-      <c r="E44" t="n">
+      <c r="E44" s="0" t="n">
         <v>0.014</v>
       </c>
       <c r="F44" s="0">
@@ -3651,7 +3651,7 @@
       <c r="D45" s="0" t="n">
         <v>0.0196</v>
       </c>
-      <c r="E45" t="n">
+      <c r="E45" s="0" t="n">
         <v>0.014</v>
       </c>
       <c r="F45" s="0">
@@ -3718,7 +3718,7 @@
       <c r="D46" s="0" t="n">
         <v>0.0196</v>
       </c>
-      <c r="E46" t="n">
+      <c r="E46" s="0" t="n">
         <v>0.014</v>
       </c>
       <c r="F46" s="0">
@@ -3785,7 +3785,7 @@
       <c r="D47" s="0" t="n">
         <v>0.0196</v>
       </c>
-      <c r="E47" t="n">
+      <c r="E47" s="0" t="n">
         <v>0.014</v>
       </c>
       <c r="F47" s="0">
@@ -3852,7 +3852,7 @@
       <c r="D48" s="0" t="n">
         <v>0.0196</v>
       </c>
-      <c r="E48" t="n">
+      <c r="E48" s="0" t="n">
         <v>0.014</v>
       </c>
       <c r="F48" s="0">
@@ -3919,7 +3919,7 @@
       <c r="D49" s="0" t="n">
         <v>0.0196</v>
       </c>
-      <c r="E49" t="n">
+      <c r="E49" s="0" t="n">
         <v>0.014</v>
       </c>
       <c r="F49" s="0">
@@ -3986,7 +3986,7 @@
       <c r="D50" s="0" t="n">
         <v>0.0196</v>
       </c>
-      <c r="E50" t="n">
+      <c r="E50" s="0" t="n">
         <v>0.014</v>
       </c>
       <c r="F50" s="0">
@@ -4053,7 +4053,7 @@
       <c r="D51" s="0" t="n">
         <v>0.0196</v>
       </c>
-      <c r="E51" t="n">
+      <c r="E51" s="0" t="n">
         <v>0.014</v>
       </c>
       <c r="F51" s="0">
@@ -4120,7 +4120,7 @@
       <c r="D52" s="0" t="n">
         <v>0.0196</v>
       </c>
-      <c r="E52" t="n">
+      <c r="E52" s="0" t="n">
         <v>0.014</v>
       </c>
       <c r="F52" s="0">
@@ -4187,7 +4187,7 @@
       <c r="D53" s="0" t="n">
         <v>0.0196</v>
       </c>
-      <c r="E53" t="n">
+      <c r="E53" s="0" t="n">
         <v>0.014</v>
       </c>
       <c r="F53" s="0">
@@ -4254,7 +4254,7 @@
       <c r="D54" s="0" t="n">
         <v>0.0196</v>
       </c>
-      <c r="E54" t="n">
+      <c r="E54" s="0" t="n">
         <v>0.014</v>
       </c>
       <c r="F54" s="0">
@@ -4321,7 +4321,7 @@
       <c r="D55" s="0" t="n">
         <v>0.0196</v>
       </c>
-      <c r="E55" t="n">
+      <c r="E55" s="0" t="n">
         <v>0.014</v>
       </c>
       <c r="F55" s="0">
@@ -4388,7 +4388,7 @@
       <c r="D56" s="0" t="n">
         <v>0.0196</v>
       </c>
-      <c r="E56" t="n">
+      <c r="E56" s="0" t="n">
         <v>0.014</v>
       </c>
       <c r="F56" s="0">
@@ -4455,7 +4455,7 @@
       <c r="D57" s="0" t="n">
         <v>0.0196</v>
       </c>
-      <c r="E57" t="n">
+      <c r="E57" s="0" t="n">
         <v>0.014</v>
       </c>
       <c r="F57" s="0">
@@ -4522,7 +4522,7 @@
       <c r="D58" s="0" t="n">
         <v>0.0196</v>
       </c>
-      <c r="E58" t="n">
+      <c r="E58" s="0" t="n">
         <v>0.014</v>
       </c>
       <c r="F58" s="0">
@@ -4589,7 +4589,7 @@
       <c r="D59" s="0" t="n">
         <v>0.0196</v>
       </c>
-      <c r="E59" t="n">
+      <c r="E59" s="0" t="n">
         <v>0.014</v>
       </c>
       <c r="F59" s="0">
@@ -4656,7 +4656,7 @@
       <c r="D60" s="0" t="n">
         <v>0.0196</v>
       </c>
-      <c r="E60" t="n">
+      <c r="E60" s="0" t="n">
         <v>0.014</v>
       </c>
       <c r="F60" s="0">
@@ -4723,7 +4723,7 @@
       <c r="D61" s="0" t="n">
         <v>0.0196</v>
       </c>
-      <c r="E61" t="n">
+      <c r="E61" s="0" t="n">
         <v>0.014</v>
       </c>
       <c r="F61" s="0">
@@ -4790,7 +4790,7 @@
       <c r="D62" s="0" t="n">
         <v>0.0196</v>
       </c>
-      <c r="E62" t="n">
+      <c r="E62" s="0" t="n">
         <v>0.014</v>
       </c>
       <c r="F62" s="0">
@@ -4857,7 +4857,7 @@
       <c r="D63" s="0" t="n">
         <v>0.0196</v>
       </c>
-      <c r="E63" t="n">
+      <c r="E63" s="0" t="n">
         <v>0.014</v>
       </c>
       <c r="F63" s="0">
@@ -4924,7 +4924,7 @@
       <c r="D64" s="0" t="n">
         <v>0.0196</v>
       </c>
-      <c r="E64" t="n">
+      <c r="E64" s="0" t="n">
         <v>0.014</v>
       </c>
       <c r="F64" s="0">
@@ -4991,7 +4991,7 @@
       <c r="D65" s="0" t="n">
         <v>0.0196</v>
       </c>
-      <c r="E65" t="n">
+      <c r="E65" s="0" t="n">
         <v>0.014</v>
       </c>
       <c r="F65" s="0">
@@ -5058,7 +5058,7 @@
       <c r="D66" s="0" t="n">
         <v>0.0196</v>
       </c>
-      <c r="E66" t="n">
+      <c r="E66" s="0" t="n">
         <v>0.014</v>
       </c>
       <c r="F66" s="0">
@@ -5125,7 +5125,7 @@
       <c r="D67" s="0" t="n">
         <v>0.0196</v>
       </c>
-      <c r="E67" t="n">
+      <c r="E67" s="0" t="n">
         <v>0.014</v>
       </c>
       <c r="F67" s="0">
@@ -5192,7 +5192,7 @@
       <c r="D68" s="0" t="n">
         <v>0.0196</v>
       </c>
-      <c r="E68" t="n">
+      <c r="E68" s="0" t="n">
         <v>0.014</v>
       </c>
       <c r="F68" s="0">
@@ -5259,7 +5259,7 @@
       <c r="D69" s="0" t="n">
         <v>0.0196</v>
       </c>
-      <c r="E69" t="n">
+      <c r="E69" s="0" t="n">
         <v>0.014</v>
       </c>
       <c r="F69" s="0">
@@ -5320,7 +5320,7 @@
       <c r="D70" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E70" t="n">
+      <c r="E70" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F70" s="0">
@@ -5381,7 +5381,7 @@
       <c r="D71" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E71" t="n">
+      <c r="E71" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F71" s="0">
@@ -5442,7 +5442,7 @@
       <c r="D72" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E72" t="n">
+      <c r="E72" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F72" s="0">
@@ -5503,7 +5503,7 @@
       <c r="D73" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E73" t="n">
+      <c r="E73" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F73" s="0">
@@ -5564,7 +5564,7 @@
       <c r="D74" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E74" t="n">
+      <c r="E74" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F74" s="0">
@@ -5625,7 +5625,7 @@
       <c r="D75" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E75" t="n">
+      <c r="E75" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F75" s="0">
@@ -5686,7 +5686,7 @@
       <c r="D76" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E76" t="n">
+      <c r="E76" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F76" s="0">
@@ -5747,7 +5747,7 @@
       <c r="D77" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E77" t="n">
+      <c r="E77" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F77" s="0">
@@ -5808,7 +5808,7 @@
       <c r="D78" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E78" t="n">
+      <c r="E78" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F78" s="0">
@@ -5869,7 +5869,7 @@
       <c r="D79" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E79" t="n">
+      <c r="E79" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F79" s="0">
@@ -5930,7 +5930,7 @@
       <c r="D80" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E80" t="n">
+      <c r="E80" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F80" s="0">
@@ -5991,7 +5991,7 @@
       <c r="D81" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E81" t="n">
+      <c r="E81" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F81" s="0">
@@ -6052,7 +6052,7 @@
       <c r="D82" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E82" t="n">
+      <c r="E82" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F82" s="0">
@@ -6113,7 +6113,7 @@
       <c r="D83" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E83" t="n">
+      <c r="E83" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F83" s="0">
@@ -6174,7 +6174,7 @@
       <c r="D84" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E84" t="n">
+      <c r="E84" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F84" s="0">
@@ -6235,7 +6235,7 @@
       <c r="D85" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E85" t="n">
+      <c r="E85" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F85" s="0">
@@ -6296,7 +6296,7 @@
       <c r="D86" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E86" t="n">
+      <c r="E86" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F86" s="0">
@@ -6357,7 +6357,7 @@
       <c r="D87" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E87" t="n">
+      <c r="E87" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F87" s="0">
@@ -6418,7 +6418,7 @@
       <c r="D88" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E88" t="n">
+      <c r="E88" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F88" s="0">
@@ -6479,7 +6479,7 @@
       <c r="D89" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E89" t="n">
+      <c r="E89" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F89" s="0">
@@ -6540,7 +6540,7 @@
       <c r="D90" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E90" t="n">
+      <c r="E90" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F90" s="0">
@@ -6601,7 +6601,7 @@
       <c r="D91" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E91" t="n">
+      <c r="E91" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F91" s="0">
@@ -6662,7 +6662,7 @@
       <c r="D92" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E92" t="n">
+      <c r="E92" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F92" s="0">
@@ -6723,7 +6723,7 @@
       <c r="D93" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E93" t="n">
+      <c r="E93" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F93" s="0">
@@ -6784,7 +6784,7 @@
       <c r="D94" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E94" t="n">
+      <c r="E94" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F94" s="0">
@@ -6845,7 +6845,7 @@
       <c r="D95" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E95" t="n">
+      <c r="E95" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F95" s="0">
@@ -6906,7 +6906,7 @@
       <c r="D96" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E96" t="n">
+      <c r="E96" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F96" s="0">
@@ -6967,7 +6967,7 @@
       <c r="D97" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E97" t="n">
+      <c r="E97" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F97" s="0">
@@ -7028,7 +7028,7 @@
       <c r="D98" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E98" t="n">
+      <c r="E98" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F98" s="0">
@@ -7089,7 +7089,7 @@
       <c r="D99" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E99" t="n">
+      <c r="E99" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F99" s="0">
@@ -7150,7 +7150,7 @@
       <c r="D100" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E100" t="n">
+      <c r="E100" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F100" s="0">
@@ -7211,7 +7211,7 @@
       <c r="D101" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E101" t="n">
+      <c r="E101" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F101" s="0">
@@ -7272,7 +7272,7 @@
       <c r="D102" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E102" t="n">
+      <c r="E102" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F102" s="0">
@@ -7333,7 +7333,7 @@
       <c r="D103" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E103" t="n">
+      <c r="E103" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F103" s="0">
@@ -7394,7 +7394,7 @@
       <c r="D104" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E104" t="n">
+      <c r="E104" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F104" s="0">
@@ -7455,7 +7455,7 @@
       <c r="D105" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E105" t="n">
+      <c r="E105" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F105" s="0">
@@ -7516,7 +7516,7 @@
       <c r="D106" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E106" t="n">
+      <c r="E106" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F106" s="0">
@@ -7577,7 +7577,7 @@
       <c r="D107" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E107" t="n">
+      <c r="E107" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F107" s="0">
@@ -7638,7 +7638,7 @@
       <c r="D108" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E108" t="n">
+      <c r="E108" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F108" s="0">
@@ -7699,7 +7699,7 @@
       <c r="D109" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E109" t="n">
+      <c r="E109" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F109" s="0">
@@ -7760,7 +7760,7 @@
       <c r="D110" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E110" t="n">
+      <c r="E110" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F110" s="0">
@@ -7821,7 +7821,7 @@
       <c r="D111" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E111" t="n">
+      <c r="E111" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F111" s="0">
@@ -7882,7 +7882,7 @@
       <c r="D112" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E112" t="n">
+      <c r="E112" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F112" s="0">
@@ -7943,7 +7943,7 @@
       <c r="D113" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E113" t="n">
+      <c r="E113" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F113" s="0">
@@ -8004,7 +8004,7 @@
       <c r="D114" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E114" t="n">
+      <c r="E114" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F114" s="0">
@@ -8065,7 +8065,7 @@
       <c r="D115" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E115" t="n">
+      <c r="E115" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F115" s="0">
@@ -8126,7 +8126,7 @@
       <c r="D116" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E116" t="n">
+      <c r="E116" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F116" s="0">
@@ -8187,7 +8187,7 @@
       <c r="D117" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E117" t="n">
+      <c r="E117" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F117" s="0">
@@ -8248,7 +8248,7 @@
       <c r="D118" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E118" t="n">
+      <c r="E118" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F118" s="0">
@@ -8309,7 +8309,7 @@
       <c r="D119" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E119" t="n">
+      <c r="E119" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F119" s="0">
@@ -8370,7 +8370,7 @@
       <c r="D120" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E120" t="n">
+      <c r="E120" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F120" s="0">
@@ -8431,7 +8431,7 @@
       <c r="D121" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E121" t="n">
+      <c r="E121" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F121" s="0">
@@ -8492,7 +8492,7 @@
       <c r="D122" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E122" t="n">
+      <c r="E122" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F122" s="0">
@@ -8553,7 +8553,7 @@
       <c r="D123" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E123" t="n">
+      <c r="E123" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F123" s="0">
@@ -8614,7 +8614,7 @@
       <c r="D124" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E124" t="n">
+      <c r="E124" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F124" s="0">
@@ -8675,7 +8675,7 @@
       <c r="D125" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E125" t="n">
+      <c r="E125" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F125" s="0">
@@ -8736,7 +8736,7 @@
       <c r="D126" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E126" t="n">
+      <c r="E126" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F126" s="0">
@@ -8797,7 +8797,7 @@
       <c r="D127" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E127" t="n">
+      <c r="E127" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F127" s="0">
@@ -8858,7 +8858,7 @@
       <c r="D128" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E128" t="n">
+      <c r="E128" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F128" s="0">
@@ -8919,7 +8919,7 @@
       <c r="D129" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E129" t="n">
+      <c r="E129" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F129" s="0">
@@ -8980,7 +8980,7 @@
       <c r="D130" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E130" t="n">
+      <c r="E130" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F130" s="0">
@@ -9041,7 +9041,7 @@
       <c r="D131" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E131" t="n">
+      <c r="E131" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F131" s="0">
@@ -9102,7 +9102,7 @@
       <c r="D132" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E132" t="n">
+      <c r="E132" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F132" s="0">
@@ -9163,7 +9163,7 @@
       <c r="D133" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E133" t="n">
+      <c r="E133" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F133" s="0">
@@ -9224,7 +9224,7 @@
       <c r="D134" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E134" t="n">
+      <c r="E134" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F134" s="0">
@@ -9285,7 +9285,7 @@
       <c r="D135" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E135" t="n">
+      <c r="E135" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F135" s="0">
@@ -9346,7 +9346,7 @@
       <c r="D136" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E136" t="n">
+      <c r="E136" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F136" s="0">
@@ -9407,7 +9407,7 @@
       <c r="D137" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E137" t="n">
+      <c r="E137" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F137" s="0">
@@ -9468,7 +9468,7 @@
       <c r="D138" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E138" t="n">
+      <c r="E138" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F138" s="0">
@@ -9529,7 +9529,7 @@
       <c r="D139" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E139" t="n">
+      <c r="E139" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F139" s="0">
@@ -9590,7 +9590,7 @@
       <c r="D140" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E140" t="n">
+      <c r="E140" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F140" s="0">
@@ -9644,7 +9644,7 @@
       <c r="D141" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E141" t="n">
+      <c r="E141" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F141" s="0">
@@ -9698,7 +9698,7 @@
       <c r="D142" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E142" t="n">
+      <c r="E142" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F142" s="0">
@@ -9752,7 +9752,7 @@
       <c r="D143" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E143" t="n">
+      <c r="E143" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F143" s="0">
@@ -9806,7 +9806,7 @@
       <c r="D144" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E144" t="n">
+      <c r="E144" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F144" s="0">
@@ -9860,7 +9860,7 @@
       <c r="D145" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E145" t="n">
+      <c r="E145" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F145" s="0">
@@ -9914,7 +9914,7 @@
       <c r="D146" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E146" t="n">
+      <c r="E146" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F146" s="0">
@@ -9968,7 +9968,7 @@
       <c r="D147" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E147" t="n">
+      <c r="E147" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F147" s="0">
@@ -10022,7 +10022,7 @@
       <c r="D148" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E148" t="n">
+      <c r="E148" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F148" s="0">
@@ -10076,7 +10076,7 @@
       <c r="D149" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E149" t="n">
+      <c r="E149" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F149" s="0">
@@ -10130,7 +10130,7 @@
       <c r="D150" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E150" t="n">
+      <c r="E150" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F150" s="0">
@@ -10184,7 +10184,7 @@
       <c r="D151" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E151" t="n">
+      <c r="E151" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F151" s="0">
@@ -10238,7 +10238,7 @@
       <c r="D152" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E152" t="n">
+      <c r="E152" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F152" s="0">
@@ -10292,7 +10292,7 @@
       <c r="D153" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E153" t="n">
+      <c r="E153" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F153" s="0">
@@ -10346,7 +10346,7 @@
       <c r="D154" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E154" t="n">
+      <c r="E154" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F154" s="0">
@@ -10400,7 +10400,7 @@
       <c r="D155" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E155" t="n">
+      <c r="E155" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F155" s="0">
@@ -10454,7 +10454,7 @@
       <c r="D156" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E156" t="n">
+      <c r="E156" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F156" s="0">
@@ -10508,7 +10508,7 @@
       <c r="D157" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E157" t="n">
+      <c r="E157" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F157" s="0">
@@ -10562,7 +10562,7 @@
       <c r="D158" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E158" t="n">
+      <c r="E158" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F158" s="0">
@@ -10616,7 +10616,7 @@
       <c r="D159" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E159" t="n">
+      <c r="E159" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F159" s="0">
@@ -10670,7 +10670,7 @@
       <c r="D160" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E160" t="n">
+      <c r="E160" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F160" s="0">
@@ -10724,7 +10724,7 @@
       <c r="D161" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E161" t="n">
+      <c r="E161" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F161" s="0">
@@ -10778,7 +10778,7 @@
       <c r="D162" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E162" t="n">
+      <c r="E162" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F162" s="0">
@@ -10832,7 +10832,7 @@
       <c r="D163" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E163" t="n">
+      <c r="E163" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F163" s="0">
@@ -10886,7 +10886,7 @@
       <c r="D164" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E164" t="n">
+      <c r="E164" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F164" s="0">
@@ -10940,7 +10940,7 @@
       <c r="D165" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E165" t="n">
+      <c r="E165" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F165" s="0">
@@ -10994,7 +10994,7 @@
       <c r="D166" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E166" t="n">
+      <c r="E166" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F166" s="0">
@@ -11048,7 +11048,7 @@
       <c r="D167" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E167" t="n">
+      <c r="E167" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F167" s="0">
@@ -11102,7 +11102,7 @@
       <c r="D168" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E168" t="n">
+      <c r="E168" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F168" s="0">
@@ -11156,7 +11156,7 @@
       <c r="D169" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E169" t="n">
+      <c r="E169" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F169" s="0">
@@ -11210,7 +11210,7 @@
       <c r="D170" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E170" t="n">
+      <c r="E170" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F170" s="0">
@@ -11264,7 +11264,7 @@
       <c r="D171" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E171" t="n">
+      <c r="E171" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F171" s="0">
@@ -11318,7 +11318,7 @@
       <c r="D172" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E172" t="n">
+      <c r="E172" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F172" s="0">
@@ -11372,7 +11372,7 @@
       <c r="D173" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E173" t="n">
+      <c r="E173" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F173" s="0">
@@ -11426,7 +11426,7 @@
       <c r="D174" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E174" t="n">
+      <c r="E174" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F174" s="0">
@@ -11480,7 +11480,7 @@
       <c r="D175" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E175" t="n">
+      <c r="E175" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F175" s="0">
@@ -11534,7 +11534,7 @@
       <c r="D176" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E176" t="n">
+      <c r="E176" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F176" s="0">
@@ -11588,7 +11588,7 @@
       <c r="D177" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E177" t="n">
+      <c r="E177" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F177" s="0">
@@ -11642,7 +11642,7 @@
       <c r="D178" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E178" t="n">
+      <c r="E178" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F178" s="0">
@@ -11696,7 +11696,7 @@
       <c r="D179" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E179" t="n">
+      <c r="E179" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F179" s="0">
@@ -11750,7 +11750,7 @@
       <c r="D180" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E180" t="n">
+      <c r="E180" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F180" s="0">
@@ -11804,7 +11804,7 @@
       <c r="D181" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E181" t="n">
+      <c r="E181" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F181" s="0">
@@ -11858,7 +11858,7 @@
       <c r="D182" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E182" t="n">
+      <c r="E182" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F182" s="0">
@@ -11912,7 +11912,7 @@
       <c r="D183" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E183" t="n">
+      <c r="E183" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F183" s="0">
@@ -11966,7 +11966,7 @@
       <c r="D184" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E184" t="n">
+      <c r="E184" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F184" s="0">
@@ -12020,7 +12020,7 @@
       <c r="D185" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E185" t="n">
+      <c r="E185" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F185" s="0">
@@ -12074,7 +12074,7 @@
       <c r="D186" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E186" t="n">
+      <c r="E186" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F186" s="0">
@@ -12128,7 +12128,7 @@
       <c r="D187" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E187" t="n">
+      <c r="E187" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F187" s="0">
@@ -12182,7 +12182,7 @@
       <c r="D188" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E188" t="n">
+      <c r="E188" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F188" s="0">
@@ -12236,7 +12236,7 @@
       <c r="D189" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E189" t="n">
+      <c r="E189" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F189" s="0">
@@ -12290,7 +12290,7 @@
       <c r="D190" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E190" t="n">
+      <c r="E190" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F190" s="0">
@@ -12344,7 +12344,7 @@
       <c r="D191" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E191" t="n">
+      <c r="E191" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F191" s="0">
@@ -12398,7 +12398,7 @@
       <c r="D192" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E192" t="n">
+      <c r="E192" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F192" s="0">
@@ -12452,7 +12452,7 @@
       <c r="D193" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E193" t="n">
+      <c r="E193" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F193" s="0">
@@ -12506,7 +12506,7 @@
       <c r="D194" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E194" t="n">
+      <c r="E194" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F194" s="0">
@@ -12560,7 +12560,7 @@
       <c r="D195" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E195" t="n">
+      <c r="E195" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F195" s="0">
@@ -12614,7 +12614,7 @@
       <c r="D196" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E196" t="n">
+      <c r="E196" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F196" s="0">
@@ -12668,7 +12668,7 @@
       <c r="D197" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E197" t="n">
+      <c r="E197" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F197" s="0">
@@ -12722,7 +12722,7 @@
       <c r="D198" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E198" t="n">
+      <c r="E198" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F198" s="0">
@@ -12776,7 +12776,7 @@
       <c r="D199" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E199" t="n">
+      <c r="E199" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F199" s="0">
@@ -12830,7 +12830,7 @@
       <c r="D200" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E200" t="n">
+      <c r="E200" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F200" s="0">
@@ -12884,7 +12884,7 @@
       <c r="D201" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E201" t="n">
+      <c r="E201" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F201" s="0">
@@ -12938,7 +12938,7 @@
       <c r="D202" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E202" t="n">
+      <c r="E202" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F202" s="0">
@@ -12992,7 +12992,7 @@
       <c r="D203" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E203" t="n">
+      <c r="E203" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F203" s="0">
@@ -13046,7 +13046,7 @@
       <c r="D204" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E204" t="n">
+      <c r="E204" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F204" s="0">
@@ -13100,7 +13100,7 @@
       <c r="D205" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E205" t="n">
+      <c r="E205" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F205" s="0">
@@ -13154,7 +13154,7 @@
       <c r="D206" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E206" t="n">
+      <c r="E206" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F206" s="0">
@@ -13208,7 +13208,7 @@
       <c r="D207" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E207" t="n">
+      <c r="E207" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F207" s="0">
@@ -13262,7 +13262,7 @@
       <c r="D208" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E208" t="n">
+      <c r="E208" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F208" s="0">
@@ -13316,7 +13316,7 @@
       <c r="D209" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E209" t="n">
+      <c r="E209" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F209" s="0">
@@ -13370,7 +13370,7 @@
       <c r="D210" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E210" t="n">
+      <c r="E210" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F210" s="0">
@@ -13424,7 +13424,7 @@
       <c r="D211" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E211" t="n">
+      <c r="E211" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F211" s="0">
@@ -13478,7 +13478,7 @@
       <c r="D212" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E212" t="n">
+      <c r="E212" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F212" s="0">
@@ -13532,7 +13532,7 @@
       <c r="D213" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E213" t="n">
+      <c r="E213" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F213" s="0">
@@ -13586,7 +13586,7 @@
       <c r="D214" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E214" t="n">
+      <c r="E214" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F214" s="0">
@@ -13640,7 +13640,7 @@
       <c r="D215" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E215" t="n">
+      <c r="E215" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F215" s="0">
@@ -13694,7 +13694,7 @@
       <c r="D216" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E216" t="n">
+      <c r="E216" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F216" s="0">
@@ -13748,7 +13748,7 @@
       <c r="D217" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E217" t="n">
+      <c r="E217" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F217" s="0">
@@ -13802,7 +13802,7 @@
       <c r="D218" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E218" t="n">
+      <c r="E218" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F218" s="0">
@@ -13856,7 +13856,7 @@
       <c r="D219" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E219" t="n">
+      <c r="E219" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F219" s="0">
@@ -13910,7 +13910,7 @@
       <c r="D220" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E220" t="n">
+      <c r="E220" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F220" s="0">
@@ -13964,7 +13964,7 @@
       <c r="D221" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E221" t="n">
+      <c r="E221" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F221" s="0">
@@ -14018,7 +14018,7 @@
       <c r="D222" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E222" t="n">
+      <c r="E222" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F222" s="0">
@@ -14072,7 +14072,7 @@
       <c r="D223" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E223" t="n">
+      <c r="E223" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F223" s="0">
@@ -14126,7 +14126,7 @@
       <c r="D224" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E224" t="n">
+      <c r="E224" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F224" s="0">
@@ -14180,7 +14180,7 @@
       <c r="D225" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E225" t="n">
+      <c r="E225" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F225" s="0">
@@ -14238,7 +14238,7 @@
       <c r="D226" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E226" t="n">
+      <c r="E226" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F226" s="0">
@@ -14292,7 +14292,7 @@
       <c r="D227" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E227" t="n">
+      <c r="E227" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F227" s="0">
@@ -14346,7 +14346,7 @@
       <c r="D228" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E228" t="n">
+      <c r="E228" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F228" s="0">
@@ -14400,7 +14400,7 @@
       <c r="D229" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E229" t="n">
+      <c r="E229" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F229" s="0">
@@ -14454,7 +14454,7 @@
       <c r="D230" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E230" t="n">
+      <c r="E230" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F230" s="0">
@@ -14508,7 +14508,7 @@
       <c r="D231" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E231" t="n">
+      <c r="E231" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F231" s="0">
@@ -14562,7 +14562,7 @@
       <c r="D232" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E232" t="n">
+      <c r="E232" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F232" s="0">
@@ -14616,7 +14616,7 @@
       <c r="D233" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E233" t="n">
+      <c r="E233" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F233" s="0">
@@ -14670,7 +14670,7 @@
       <c r="D234" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E234" t="n">
+      <c r="E234" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F234" s="0">
@@ -14724,7 +14724,7 @@
       <c r="D235" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E235" t="n">
+      <c r="E235" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F235" s="0">
@@ -14778,7 +14778,7 @@
       <c r="D236" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E236" t="n">
+      <c r="E236" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F236" s="0">
@@ -14832,7 +14832,7 @@
       <c r="D237" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E237" t="n">
+      <c r="E237" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F237" s="0">
@@ -14886,7 +14886,7 @@
       <c r="D238" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E238" t="n">
+      <c r="E238" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F238" s="0">
@@ -14940,7 +14940,7 @@
       <c r="D239" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E239" t="n">
+      <c r="E239" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F239" s="0">
@@ -14994,7 +14994,7 @@
       <c r="D240" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E240" t="n">
+      <c r="E240" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F240" s="0">
@@ -15048,7 +15048,7 @@
       <c r="D241" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E241" t="n">
+      <c r="E241" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F241" s="0">
@@ -15102,7 +15102,7 @@
       <c r="D242" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E242" t="n">
+      <c r="E242" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F242" s="0">
@@ -15156,7 +15156,7 @@
       <c r="D243" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E243" t="n">
+      <c r="E243" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F243" s="0">
@@ -15210,7 +15210,7 @@
       <c r="D244" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E244" t="n">
+      <c r="E244" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F244" s="0">
@@ -15264,7 +15264,7 @@
       <c r="D245" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E245" t="n">
+      <c r="E245" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F245" s="0">
@@ -15318,7 +15318,7 @@
       <c r="D246" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E246" t="n">
+      <c r="E246" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F246" s="0">
@@ -15372,7 +15372,7 @@
       <c r="D247" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E247" t="n">
+      <c r="E247" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F247" s="0">
@@ -15426,7 +15426,7 @@
       <c r="D248" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E248" t="n">
+      <c r="E248" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F248" s="0">
@@ -15480,7 +15480,7 @@
       <c r="D249" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E249" t="n">
+      <c r="E249" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F249" s="0">
@@ -15534,7 +15534,7 @@
       <c r="D250" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E250" t="n">
+      <c r="E250" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F250" s="0">
@@ -15588,7 +15588,7 @@
       <c r="D251" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E251" t="n">
+      <c r="E251" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F251" s="0">
@@ -15642,7 +15642,7 @@
       <c r="D252" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E252" t="n">
+      <c r="E252" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F252" s="0">
@@ -15696,7 +15696,7 @@
       <c r="D253" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E253" t="n">
+      <c r="E253" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F253" s="0">
@@ -15750,7 +15750,7 @@
       <c r="D254" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E254" t="n">
+      <c r="E254" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F254" s="0">
@@ -15804,7 +15804,7 @@
       <c r="D255" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E255" t="n">
+      <c r="E255" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F255" s="0">
@@ -15858,7 +15858,7 @@
       <c r="D256" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E256" t="n">
+      <c r="E256" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F256" s="0">
@@ -15912,7 +15912,7 @@
       <c r="D257" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E257" t="n">
+      <c r="E257" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F257" s="0">
@@ -15966,7 +15966,7 @@
       <c r="D258" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E258" t="n">
+      <c r="E258" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F258" s="0">
@@ -16020,7 +16020,7 @@
       <c r="D259" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E259" t="n">
+      <c r="E259" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F259" s="0">
@@ -16074,7 +16074,7 @@
       <c r="D260" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E260" t="n">
+      <c r="E260" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F260" s="0">
@@ -16128,7 +16128,7 @@
       <c r="D261" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E261" t="n">
+      <c r="E261" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F261" s="0">
@@ -16182,7 +16182,7 @@
       <c r="D262" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E262" t="n">
+      <c r="E262" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F262" s="0">
@@ -16236,7 +16236,7 @@
       <c r="D263" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E263" t="n">
+      <c r="E263" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F263" s="0">
@@ -16290,7 +16290,7 @@
       <c r="D264" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E264" t="n">
+      <c r="E264" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F264" s="0">
@@ -16344,7 +16344,7 @@
       <c r="D265" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E265" t="n">
+      <c r="E265" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F265" s="0">
@@ -16398,7 +16398,7 @@
       <c r="D266" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E266" t="n">
+      <c r="E266" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F266" s="0">
@@ -16452,7 +16452,7 @@
       <c r="D267" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E267" t="n">
+      <c r="E267" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F267" s="0">
@@ -16506,7 +16506,7 @@
       <c r="D268" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E268" t="n">
+      <c r="E268" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F268" s="0">
@@ -16560,7 +16560,7 @@
       <c r="D269" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E269" t="n">
+      <c r="E269" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F269" s="0">
@@ -16614,7 +16614,7 @@
       <c r="D270" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E270" t="n">
+      <c r="E270" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F270" s="0">
@@ -16668,7 +16668,7 @@
       <c r="D271" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E271" t="n">
+      <c r="E271" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F271" s="0">
@@ -16722,7 +16722,7 @@
       <c r="D272" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E272" t="n">
+      <c r="E272" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F272" s="0">
@@ -16776,7 +16776,7 @@
       <c r="D273" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E273" t="n">
+      <c r="E273" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F273" s="0">
@@ -16830,7 +16830,7 @@
       <c r="D274" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E274" t="n">
+      <c r="E274" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F274" s="0">
@@ -16884,7 +16884,7 @@
       <c r="D275" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E275" t="n">
+      <c r="E275" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F275" s="0">
@@ -16938,7 +16938,7 @@
       <c r="D276" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E276" t="n">
+      <c r="E276" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F276" s="0">
@@ -16992,7 +16992,7 @@
       <c r="D277" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E277" t="n">
+      <c r="E277" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F277" s="0">
@@ -17046,7 +17046,7 @@
       <c r="D278" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E278" t="n">
+      <c r="E278" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F278" s="0">
@@ -17100,7 +17100,7 @@
       <c r="D279" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E279" t="n">
+      <c r="E279" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F279" s="0">
@@ -17154,7 +17154,7 @@
       <c r="D280" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E280" t="n">
+      <c r="E280" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F280" s="0">
@@ -17208,7 +17208,7 @@
       <c r="D281" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E281" t="n">
+      <c r="E281" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F281" s="0">
@@ -17262,7 +17262,7 @@
       <c r="D282" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E282" t="n">
+      <c r="E282" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F282" s="0">
@@ -17316,7 +17316,7 @@
       <c r="D283" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E283" t="n">
+      <c r="E283" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F283" s="0">
@@ -17370,7 +17370,7 @@
       <c r="D284" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E284" t="n">
+      <c r="E284" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F284" s="0">
@@ -17424,7 +17424,7 @@
       <c r="D285" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E285" t="n">
+      <c r="E285" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F285" s="0">
@@ -17478,7 +17478,7 @@
       <c r="D286" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E286" t="n">
+      <c r="E286" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F286" s="0">
@@ -17532,7 +17532,7 @@
       <c r="D287" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E287" t="n">
+      <c r="E287" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F287" s="0">
@@ -17586,7 +17586,7 @@
       <c r="D288" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E288" t="n">
+      <c r="E288" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F288" s="0">
@@ -17640,7 +17640,7 @@
       <c r="D289" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E289" t="n">
+      <c r="E289" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F289" s="0">
@@ -17694,7 +17694,7 @@
       <c r="D290" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E290" t="n">
+      <c r="E290" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F290" s="0">
@@ -17748,7 +17748,7 @@
       <c r="D291" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E291" t="n">
+      <c r="E291" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F291" s="0">
@@ -17802,7 +17802,7 @@
       <c r="D292" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E292" t="n">
+      <c r="E292" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F292" s="0">
@@ -17856,7 +17856,7 @@
       <c r="D293" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E293" t="n">
+      <c r="E293" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F293" s="0">
@@ -17910,7 +17910,7 @@
       <c r="D294" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E294" t="n">
+      <c r="E294" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F294" s="0">
@@ -17964,7 +17964,7 @@
       <c r="D295" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E295" t="n">
+      <c r="E295" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F295" s="0">
@@ -18018,7 +18018,7 @@
       <c r="D296" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E296" t="n">
+      <c r="E296" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F296" s="0">
@@ -18072,7 +18072,7 @@
       <c r="D297" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E297" t="n">
+      <c r="E297" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F297" s="0">
@@ -18126,7 +18126,7 @@
       <c r="D298" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E298" t="n">
+      <c r="E298" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F298" s="0">
@@ -18180,7 +18180,7 @@
       <c r="D299" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E299" t="n">
+      <c r="E299" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F299" s="0">
@@ -18234,7 +18234,7 @@
       <c r="D300" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E300" t="n">
+      <c r="E300" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F300" s="0">
@@ -18288,7 +18288,7 @@
       <c r="D301" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E301" t="n">
+      <c r="E301" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F301" s="0">
@@ -18342,7 +18342,7 @@
       <c r="D302" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E302" t="n">
+      <c r="E302" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F302" s="0">
@@ -18396,7 +18396,7 @@
       <c r="D303" s="0" t="n">
         <v>0.0191</v>
       </c>
-      <c r="E303" t="n">
+      <c r="E303" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F303" s="0">
@@ -18494,7 +18494,7 @@
       <c r="C2" s="0" t="n">
         <v>0.846</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D2" s="0" t="n">
         <v>0.02188474498689175</v>
       </c>
       <c r="E2" s="0">
@@ -18529,7 +18529,7 @@
       <c r="C3" s="0" t="n">
         <v>0.837</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D3" s="0" t="n">
         <v>0.0200420618057251</v>
       </c>
       <c r="E3" s="0">
@@ -18564,7 +18564,7 @@
       <c r="C4" s="0" t="n">
         <v>0.828</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D4" s="0" t="n">
         <v>0.0202435664832592</v>
       </c>
       <c r="E4" s="0">
@@ -18599,7 +18599,7 @@
       <c r="C5" s="0" t="n">
         <v>0.8179999999999999</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D5" s="0" t="n">
         <v>0.01856775023043156</v>
       </c>
       <c r="E5" s="0">
@@ -18634,7 +18634,7 @@
       <c r="C6" s="0" t="n">
         <v>0.8110000000000001</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D6" s="0" t="n">
         <v>0.02292344346642494</v>
       </c>
       <c r="E6" s="0">
@@ -18669,7 +18669,7 @@
       <c r="C7" s="0" t="n">
         <v>0.803</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D7" s="0" t="n">
         <v>0.02005913108587265</v>
       </c>
       <c r="E7" s="0">
@@ -18704,7 +18704,7 @@
       <c r="C8" s="0" t="n">
         <v>0.797</v>
       </c>
-      <c r="D8" t="n">
+      <c r="D8" s="0" t="n">
         <v>0.02002382278442383</v>
       </c>
       <c r="E8" s="0">
@@ -18739,7 +18739,7 @@
       <c r="C9" s="0" t="n">
         <v>0.791</v>
       </c>
-      <c r="D9" t="n">
+      <c r="D9" s="0" t="n">
         <v>0.02062098495662212</v>
       </c>
       <c r="E9" s="0">
@@ -18774,7 +18774,7 @@
       <c r="C10" s="0" t="n">
         <v>0.785</v>
       </c>
-      <c r="D10" t="n">
+      <c r="D10" s="0" t="n">
         <v>0.02150164172053337</v>
       </c>
       <c r="E10" s="0">
@@ -18809,7 +18809,7 @@
       <c r="C11" s="0" t="n">
         <v>0.779</v>
       </c>
-      <c r="D11" t="n">
+      <c r="D11" s="0" t="n">
         <v>0.02074512094259262</v>
       </c>
       <c r="E11" s="0">
@@ -18844,7 +18844,7 @@
       <c r="C12" s="0" t="n">
         <v>0.774</v>
       </c>
-      <c r="D12" t="n">
+      <c r="D12" s="0" t="n">
         <v>0.02223155833780766</v>
       </c>
       <c r="E12" s="0">
@@ -18879,7 +18879,7 @@
       <c r="C13" s="0" t="n">
         <v>0.768</v>
       </c>
-      <c r="D13" t="n">
+      <c r="D13" s="0" t="n">
         <v>0.02061885595321655</v>
       </c>
       <c r="E13" s="0">
@@ -18914,7 +18914,7 @@
       <c r="C14" s="0" t="n">
         <v>0.764</v>
       </c>
-      <c r="D14" t="n">
+      <c r="D14" s="0" t="n">
         <v>0.02157804369926453</v>
       </c>
       <c r="E14" s="0">
@@ -18949,7 +18949,7 @@
       <c r="C15" s="0" t="n">
         <v>0.759</v>
       </c>
-      <c r="D15" t="n">
+      <c r="D15" s="0" t="n">
         <v>0.02084491401910782</v>
       </c>
       <c r="E15" s="0">
@@ -18984,7 +18984,7 @@
       <c r="C16" s="0" t="n">
         <v>0.754</v>
       </c>
-      <c r="D16" t="n">
+      <c r="D16" s="0" t="n">
         <v>0.02178681455552578</v>
       </c>
       <c r="E16" s="0">
@@ -19019,7 +19019,7 @@
       <c r="C17" s="0" t="n">
         <v>0.75</v>
       </c>
-      <c r="D17" t="n">
+      <c r="D17" s="0" t="n">
         <v>0.02149804309010506</v>
       </c>
       <c r="E17" s="0">
@@ -19054,7 +19054,7 @@
       <c r="C18" s="0" t="n">
         <v>0.746</v>
       </c>
-      <c r="D18" t="n">
+      <c r="D18" s="0" t="n">
         <v>0.02160311862826347</v>
       </c>
       <c r="E18" s="0">
@@ -19089,7 +19089,7 @@
       <c r="C19" s="0" t="n">
         <v>0.742</v>
       </c>
-      <c r="D19" t="n">
+      <c r="D19" s="0" t="n">
         <v>0.02212035283446312</v>
       </c>
       <c r="E19" s="0">
@@ -19124,7 +19124,7 @@
       <c r="C20" s="0" t="n">
         <v>0.737</v>
       </c>
-      <c r="D20" t="n">
+      <c r="D20" s="0" t="n">
         <v>0.02196707017719746</v>
       </c>
       <c r="E20" s="0">
@@ -19159,7 +19159,7 @@
       <c r="C21" s="0" t="n">
         <v>0.733</v>
       </c>
-      <c r="D21" t="n">
+      <c r="D21" s="0" t="n">
         <v>0.02210067585110664</v>
       </c>
       <c r="E21" s="0">
@@ -19194,7 +19194,7 @@
       <c r="C22" s="0" t="n">
         <v>0.729</v>
       </c>
-      <c r="D22" t="n">
+      <c r="D22" s="0" t="n">
         <v>0.02124469913542271</v>
       </c>
       <c r="E22" s="0">
@@ -19229,7 +19229,7 @@
       <c r="C23" s="0" t="n">
         <v>0.726</v>
       </c>
-      <c r="D23" t="n">
+      <c r="D23" s="0" t="n">
         <v>0.02223465405404568</v>
       </c>
       <c r="E23" s="0">
@@ -19264,7 +19264,7 @@
       <c r="C24" s="0" t="n">
         <v>0.722</v>
       </c>
-      <c r="D24" t="n">
+      <c r="D24" s="0" t="n">
         <v>0.02199913933873177</v>
       </c>
       <c r="E24" s="0">
@@ -19299,7 +19299,7 @@
       <c r="C25" s="0" t="n">
         <v>0.718</v>
       </c>
-      <c r="D25" t="n">
+      <c r="D25" s="0" t="n">
         <v>0.0226028598845005</v>
       </c>
       <c r="E25" s="0">
@@ -19334,7 +19334,7 @@
       <c r="C26" s="0" t="n">
         <v>0.714</v>
       </c>
-      <c r="D26" t="n">
+      <c r="D26" s="0" t="n">
         <v>0.02136674337089062</v>
       </c>
       <c r="E26" s="0">
@@ -19369,7 +19369,7 @@
       <c r="C27" s="0" t="n">
         <v>0.711</v>
       </c>
-      <c r="D27" t="n">
+      <c r="D27" s="0" t="n">
         <v>0.02244500815868378</v>
       </c>
       <c r="E27" s="0">
@@ -19404,7 +19404,7 @@
       <c r="C28" s="0" t="n">
         <v>0.707</v>
       </c>
-      <c r="D28" t="n">
+      <c r="D28" s="0" t="n">
         <v>0.02068980224430561</v>
       </c>
       <c r="E28" s="0">
@@ -19439,7 +19439,7 @@
       <c r="C29" s="0" t="n">
         <v>0.704</v>
       </c>
-      <c r="D29" t="n">
+      <c r="D29" s="0" t="n">
         <v>0.0218848567456007</v>
       </c>
       <c r="E29" s="0">
@@ -19474,7 +19474,7 @@
       <c r="C30" s="0" t="n">
         <v>0.701</v>
       </c>
-      <c r="D30" t="n">
+      <c r="D30" s="0" t="n">
         <v>0.02142326533794403</v>
       </c>
       <c r="E30" s="0">
@@ -19509,7 +19509,7 @@
       <c r="C31" s="0" t="n">
         <v>0.697</v>
       </c>
-      <c r="D31" t="n">
+      <c r="D31" s="0" t="n">
         <v>0.02206030488014221</v>
       </c>
       <c r="E31" s="0">
@@ -19544,7 +19544,7 @@
       <c r="C32" s="0" t="n">
         <v>0.694</v>
       </c>
-      <c r="D32" t="n">
+      <c r="D32" s="0" t="n">
         <v>0.02066031657159328</v>
       </c>
       <c r="E32" s="0">
@@ -19579,7 +19579,7 @@
       <c r="C33" s="0" t="n">
         <v>0.6909999999999999</v>
       </c>
-      <c r="D33" t="n">
+      <c r="D33" s="0" t="n">
         <v>0.02202636934816837</v>
       </c>
       <c r="E33" s="0">
@@ -19614,7 +19614,7 @@
       <c r="C34" s="0" t="n">
         <v>0.6870000000000001</v>
       </c>
-      <c r="D34" t="n">
+      <c r="D34" s="0" t="n">
         <v>0.02086247317492962</v>
       </c>
       <c r="E34" s="0">
@@ -19649,7 +19649,7 @@
       <c r="C35" s="0" t="n">
         <v>0.6840000000000001</v>
       </c>
-      <c r="D35" t="n">
+      <c r="D35" s="0" t="n">
         <v>0.02169629000127316</v>
       </c>
       <c r="E35" s="0">
@@ -19684,7 +19684,7 @@
       <c r="C36" s="0" t="n">
         <v>0.681</v>
       </c>
-      <c r="D36" t="n">
+      <c r="D36" s="0" t="n">
         <v>0.02072627283632755</v>
       </c>
       <c r="E36" s="0">
@@ -19719,7 +19719,7 @@
       <c r="C37" s="0" t="n">
         <v>0.678</v>
       </c>
-      <c r="D37" t="n">
+      <c r="D37" s="0" t="n">
         <v>0.02208458632230759</v>
       </c>
       <c r="E37" s="0">
@@ -19754,7 +19754,7 @@
       <c r="C38" s="0" t="n">
         <v>0.675</v>
       </c>
-      <c r="D38" t="n">
+      <c r="D38" s="0" t="n">
         <v>0.02080466970801353</v>
       </c>
       <c r="E38" s="0">
@@ -19789,7 +19789,7 @@
       <c r="C39" s="0" t="n">
         <v>0.672</v>
       </c>
-      <c r="D39" t="n">
+      <c r="D39" s="0" t="n">
         <v>0.02198246121406555</v>
       </c>
       <c r="E39" s="0">
@@ -19824,7 +19824,7 @@
       <c r="C40" s="0" t="n">
         <v>0.669</v>
       </c>
-      <c r="D40" t="n">
+      <c r="D40" s="0" t="n">
         <v>0.0207621343433857</v>
       </c>
       <c r="E40" s="0">
@@ -19859,7 +19859,7 @@
       <c r="C41" s="0" t="n">
         <v>0.666</v>
       </c>
-      <c r="D41" t="n">
+      <c r="D41" s="0" t="n">
         <v>0.02174874022603035</v>
       </c>
       <c r="E41" s="0">
@@ -19894,7 +19894,7 @@
       <c r="C42" s="0" t="n">
         <v>0.663</v>
       </c>
-      <c r="D42" t="n">
+      <c r="D42" s="0" t="n">
         <v>0.02079889923334122</v>
       </c>
       <c r="E42" s="0">
@@ -19929,7 +19929,7 @@
       <c r="C43" s="0" t="n">
         <v>0.66</v>
       </c>
-      <c r="D43" t="n">
+      <c r="D43" s="0" t="n">
         <v>0.02128463797271252</v>
       </c>
       <c r="E43" s="0">
@@ -19964,7 +19964,7 @@
       <c r="C44" s="0" t="n">
         <v>0.657</v>
       </c>
-      <c r="D44" t="n">
+      <c r="D44" s="0" t="n">
         <v>0.02105836756527424</v>
       </c>
       <c r="E44" s="0">
@@ -19999,7 +19999,7 @@
       <c r="C45" s="0" t="n">
         <v>0.654</v>
       </c>
-      <c r="D45" t="n">
+      <c r="D45" s="0" t="n">
         <v>0.02128434740006924</v>
       </c>
       <c r="E45" s="0">
@@ -20034,7 +20034,7 @@
       <c r="C46" s="0" t="n">
         <v>0.651</v>
       </c>
-      <c r="D46" t="n">
+      <c r="D46" s="0" t="n">
         <v>0.02171558514237404</v>
       </c>
       <c r="E46" s="0">
@@ -20069,7 +20069,7 @@
       <c r="C47" s="0" t="n">
         <v>0.648</v>
       </c>
-      <c r="D47" t="n">
+      <c r="D47" s="0" t="n">
         <v>0.02162325009703636</v>
       </c>
       <c r="E47" s="0">
@@ -20104,7 +20104,7 @@
       <c r="C48" s="0" t="n">
         <v>0.646</v>
       </c>
-      <c r="D48" t="n">
+      <c r="D48" s="0" t="n">
         <v>0.02090091444551945</v>
       </c>
       <c r="E48" s="0">
@@ -20139,7 +20139,7 @@
       <c r="C49" s="0" t="n">
         <v>0.643</v>
       </c>
-      <c r="D49" t="n">
+      <c r="D49" s="0" t="n">
         <v>0.02139896526932716</v>
       </c>
       <c r="E49" s="0">
@@ -20174,7 +20174,7 @@
       <c r="C50" s="0" t="n">
         <v>0.64</v>
       </c>
-      <c r="D50" t="n">
+      <c r="D50" s="0" t="n">
         <v>0.02111426182091236</v>
       </c>
       <c r="E50" s="0">
@@ -20209,7 +20209,7 @@
       <c r="C51" s="0" t="n">
         <v>0.637</v>
       </c>
-      <c r="D51" t="n">
+      <c r="D51" s="0" t="n">
         <v>0.02089146338403225</v>
       </c>
       <c r="E51" s="0">
@@ -20244,7 +20244,7 @@
       <c r="C52" s="0" t="n">
         <v>0.634</v>
       </c>
-      <c r="D52" t="n">
+      <c r="D52" s="0" t="n">
         <v>0.02088642492890358</v>
       </c>
       <c r="E52" s="0">
@@ -20279,7 +20279,7 @@
       <c r="C53" s="0" t="n">
         <v>0.631</v>
       </c>
-      <c r="D53" t="n">
+      <c r="D53" s="0" t="n">
         <v>0.02163968607783318</v>
       </c>
       <c r="E53" s="0">
@@ -20314,7 +20314,7 @@
       <c r="C54" s="0" t="n">
         <v>0.629</v>
       </c>
-      <c r="D54" t="n">
+      <c r="D54" s="0" t="n">
         <v>0.0208536833524704</v>
       </c>
       <c r="E54" s="0">
@@ -20349,7 +20349,7 @@
       <c r="C55" s="0" t="n">
         <v>0.626</v>
       </c>
-      <c r="D55" t="n">
+      <c r="D55" s="0" t="n">
         <v>0.02042403817176819</v>
       </c>
       <c r="E55" s="0">
@@ -20384,7 +20384,7 @@
       <c r="C56" s="0" t="n">
         <v>0.623</v>
       </c>
-      <c r="D56" t="n">
+      <c r="D56" s="0" t="n">
         <v>0.02127382904291153</v>
       </c>
       <c r="E56" s="0">
@@ -20419,7 +20419,7 @@
       <c r="C57" s="0" t="n">
         <v>0.621</v>
       </c>
-      <c r="D57" t="n">
+      <c r="D57" s="0" t="n">
         <v>0.02156965248286724</v>
       </c>
       <c r="E57" s="0">
@@ -20454,7 +20454,7 @@
       <c r="C58" s="0" t="n">
         <v>0.618</v>
       </c>
-      <c r="D58" t="n">
+      <c r="D58" s="0" t="n">
         <v>0.0206918828189373</v>
       </c>
       <c r="E58" s="0">
@@ -20489,7 +20489,7 @@
       <c r="C59" s="0" t="n">
         <v>0.615</v>
       </c>
-      <c r="D59" t="n">
+      <c r="D59" s="0" t="n">
         <v>0.02107076346874237</v>
       </c>
       <c r="E59" s="0">
@@ -20524,7 +20524,7 @@
       <c r="C60" s="0" t="n">
         <v>0.613</v>
       </c>
-      <c r="D60" t="n">
+      <c r="D60" s="0" t="n">
         <v>0.02087909355759621</v>
       </c>
       <c r="E60" s="0">
@@ -20559,7 +20559,7 @@
       <c r="C61" s="0" t="n">
         <v>0.61</v>
       </c>
-      <c r="D61" t="n">
+      <c r="D61" s="0" t="n">
         <v>0.02139941975474358</v>
       </c>
       <c r="E61" s="0">
@@ -20594,7 +20594,7 @@
       <c r="C62" s="0" t="n">
         <v>0.608</v>
       </c>
-      <c r="D62" t="n">
+      <c r="D62" s="0" t="n">
         <v>0.02168705686926842</v>
       </c>
       <c r="E62" s="0">
@@ -20629,7 +20629,7 @@
       <c r="C63" s="0" t="n">
         <v>0.605</v>
       </c>
-      <c r="D63" t="n">
+      <c r="D63" s="0" t="n">
         <v>0.02088871784508228</v>
       </c>
       <c r="E63" s="0">
@@ -20664,7 +20664,7 @@
       <c r="C64" s="0" t="n">
         <v>0.603</v>
       </c>
-      <c r="D64" t="n">
+      <c r="D64" s="0" t="n">
         <v>0.02038130722939968</v>
       </c>
       <c r="E64" s="0">
@@ -20699,7 +20699,7 @@
       <c r="C65" s="0" t="n">
         <v>0.6</v>
       </c>
-      <c r="D65" t="n">
+      <c r="D65" s="0" t="n">
         <v>0.02090147696435452</v>
       </c>
       <c r="E65" s="0">
@@ -20734,7 +20734,7 @@
       <c r="C66" s="0" t="n">
         <v>0.597</v>
       </c>
-      <c r="D66" t="n">
+      <c r="D66" s="0" t="n">
         <v>0.02089935913681984</v>
       </c>
       <c r="E66" s="0">
@@ -20769,7 +20769,7 @@
       <c r="C67" s="0" t="n">
         <v>0.595</v>
       </c>
-      <c r="D67" t="n">
+      <c r="D67" s="0" t="n">
         <v>0.02123693376779556</v>
       </c>
       <c r="E67" s="0">
@@ -20804,7 +20804,7 @@
       <c r="C68" s="0" t="n">
         <v>0.592</v>
       </c>
-      <c r="D68" t="n">
+      <c r="D68" s="0" t="n">
         <v>0.02121633850038052</v>
       </c>
       <c r="E68" s="0">
@@ -20839,7 +20839,7 @@
       <c r="C69" s="0" t="n">
         <v>0.59</v>
       </c>
-      <c r="D69" t="n">
+      <c r="D69" s="0" t="n">
         <v>0.02192088775336742</v>
       </c>
       <c r="E69" s="0">
@@ -20874,7 +20874,7 @@
       <c r="C70" s="0" t="n">
         <v>0.587</v>
       </c>
-      <c r="D70" t="n">
+      <c r="D70" s="0" t="n">
         <v>0.02134180627763271</v>
       </c>
       <c r="E70" s="0">
@@ -20909,7 +20909,7 @@
       <c r="C71" s="0" t="n">
         <v>0.585</v>
       </c>
-      <c r="D71" t="n">
+      <c r="D71" s="0" t="n">
         <v>0.02118257060647011</v>
       </c>
       <c r="E71" s="0">
@@ -20944,7 +20944,7 @@
       <c r="C72" s="0" t="n">
         <v>0.582</v>
       </c>
-      <c r="D72" t="n">
+      <c r="D72" s="0" t="n">
         <v>0.02070923149585724</v>
       </c>
       <c r="E72" s="0">
@@ -20979,7 +20979,7 @@
       <c r="C73" s="0" t="n">
         <v>0.58</v>
       </c>
-      <c r="D73" t="n">
+      <c r="D73" s="0" t="n">
         <v>0.02084982767701149</v>
       </c>
       <c r="E73" s="0">
@@ -21014,7 +21014,7 @@
       <c r="C74" s="0" t="n">
         <v>0.578</v>
       </c>
-      <c r="D74" t="n">
+      <c r="D74" s="0" t="n">
         <v>0.02178002707660198</v>
       </c>
       <c r="E74" s="0">
@@ -21049,7 +21049,7 @@
       <c r="C75" s="0" t="n">
         <v>0.575</v>
       </c>
-      <c r="D75" t="n">
+      <c r="D75" s="0" t="n">
         <v>0.0216306746006012</v>
       </c>
       <c r="E75" s="0">
@@ -21084,7 +21084,7 @@
       <c r="C76" s="0" t="n">
         <v>0.573</v>
       </c>
-      <c r="D76" t="n">
+      <c r="D76" s="0" t="n">
         <v>0.0215228870511055</v>
       </c>
       <c r="E76" s="0">
@@ -21119,7 +21119,7 @@
       <c r="C77" s="0" t="n">
         <v>0.57</v>
       </c>
-      <c r="D77" t="n">
+      <c r="D77" s="0" t="n">
         <v>0.02099636942148209</v>
       </c>
       <c r="E77" s="0">
@@ -21154,7 +21154,7 @@
       <c r="C78" s="0" t="n">
         <v>0.5679999999999999</v>
       </c>
-      <c r="D78" t="n">
+      <c r="D78" s="0" t="n">
         <v>0.02120652794837952</v>
       </c>
       <c r="E78" s="0">
@@ -21189,7 +21189,7 @@
       <c r="C79" s="0" t="n">
         <v>0.5649999999999999</v>
       </c>
-      <c r="D79" t="n">
+      <c r="D79" s="0" t="n">
         <v>0.02128704264760017</v>
       </c>
       <c r="E79" s="0">
@@ -21224,7 +21224,7 @@
       <c r="C80" s="0" t="n">
         <v>0.5629999999999999</v>
       </c>
-      <c r="D80" t="n">
+      <c r="D80" s="0" t="n">
         <v>0.0215698704123497</v>
       </c>
       <c r="E80" s="0">
@@ -21259,7 +21259,7 @@
       <c r="C81" s="0" t="n">
         <v>0.5610000000000001</v>
       </c>
-      <c r="D81" t="n">
+      <c r="D81" s="0" t="n">
         <v>0.02135146409273148</v>
       </c>
       <c r="E81" s="0">
@@ -21294,7 +21294,7 @@
       <c r="C82" s="0" t="n">
         <v>0.5580000000000001</v>
       </c>
-      <c r="D82" t="n">
+      <c r="D82" s="0" t="n">
         <v>0.02219929546117783</v>
       </c>
       <c r="E82" s="0">
@@ -21329,7 +21329,7 @@
       <c r="C83" s="0" t="n">
         <v>0.556</v>
       </c>
-      <c r="D83" t="n">
+      <c r="D83" s="0" t="n">
         <v>0.02134930714964867</v>
       </c>
       <c r="E83" s="0">
@@ -21364,7 +21364,7 @@
       <c r="C84" s="0" t="n">
         <v>0.554</v>
       </c>
-      <c r="D84" t="n">
+      <c r="D84" s="0" t="n">
         <v>0.0212129782885313</v>
       </c>
       <c r="E84" s="0">
@@ -21399,7 +21399,7 @@
       <c r="C85" s="0" t="n">
         <v>0.551</v>
       </c>
-      <c r="D85" t="n">
+      <c r="D85" s="0" t="n">
         <v>0.02233623340725899</v>
       </c>
       <c r="E85" s="0">
@@ -21434,7 +21434,7 @@
       <c r="C86" s="0" t="n">
         <v>0.549</v>
       </c>
-      <c r="D86" t="n">
+      <c r="D86" s="0" t="n">
         <v>0.0209533553570509</v>
       </c>
       <c r="E86" s="0">
@@ -21469,7 +21469,7 @@
       <c r="C87" s="0" t="n">
         <v>0.546</v>
       </c>
-      <c r="D87" t="n">
+      <c r="D87" s="0" t="n">
         <v>0.02204925194382668</v>
       </c>
       <c r="E87" s="0">
@@ -21504,7 +21504,7 @@
       <c r="C88" s="0" t="n">
         <v>0.544</v>
       </c>
-      <c r="D88" t="n">
+      <c r="D88" s="0" t="n">
         <v>0.02171573415398598</v>
       </c>
       <c r="E88" s="0">
@@ -21539,7 +21539,7 @@
       <c r="C89" s="0" t="n">
         <v>0.542</v>
       </c>
-      <c r="D89" t="n">
+      <c r="D89" s="0" t="n">
         <v>0.0216961745172739</v>
       </c>
       <c r="E89" s="0">
@@ -21574,7 +21574,7 @@
       <c r="C90" s="0" t="n">
         <v>0.539</v>
       </c>
-      <c r="D90" t="n">
+      <c r="D90" s="0" t="n">
         <v>0.02190676517784595</v>
       </c>
       <c r="E90" s="0">
@@ -21609,7 +21609,7 @@
       <c r="C91" s="0" t="n">
         <v>0.537</v>
       </c>
-      <c r="D91" t="n">
+      <c r="D91" s="0" t="n">
         <v>0.02175609022378922</v>
       </c>
       <c r="E91" s="0">
@@ -21644,7 +21644,7 @@
       <c r="C92" s="0" t="n">
         <v>0.534</v>
       </c>
-      <c r="D92" t="n">
+      <c r="D92" s="0" t="n">
         <v>0.02242948859930038</v>
       </c>
       <c r="E92" s="0">
@@ -21679,7 +21679,7 @@
       <c r="C93" s="0" t="n">
         <v>0.533</v>
       </c>
-      <c r="D93" t="n">
+      <c r="D93" s="0" t="n">
         <v>0.0215414147824049</v>
       </c>
       <c r="E93" s="0">
@@ -21714,7 +21714,7 @@
       <c r="C94" s="0" t="n">
         <v>0.53</v>
       </c>
-      <c r="D94" t="n">
+      <c r="D94" s="0" t="n">
         <v>0.02252337895333767</v>
       </c>
       <c r="E94" s="0">
@@ -21749,7 +21749,7 @@
       <c r="C95" s="0" t="n">
         <v>0.528</v>
       </c>
-      <c r="D95" t="n">
+      <c r="D95" s="0" t="n">
         <v>0.02160502783954144</v>
       </c>
       <c r="E95" s="0">
@@ -21784,7 +21784,7 @@
       <c r="C96" s="0" t="n">
         <v>0.526</v>
       </c>
-      <c r="D96" t="n">
+      <c r="D96" s="0" t="n">
         <v>0.02235906384885311</v>
       </c>
       <c r="E96" s="0">
@@ -21819,7 +21819,7 @@
       <c r="C97" s="0" t="n">
         <v>0.524</v>
       </c>
-      <c r="D97" t="n">
+      <c r="D97" s="0" t="n">
         <v>0.0217084027826786</v>
       </c>
       <c r="E97" s="0">
@@ -21854,7 +21854,7 @@
       <c r="C98" s="0" t="n">
         <v>0.521</v>
       </c>
-      <c r="D98" t="n">
+      <c r="D98" s="0" t="n">
         <v>0.02225402183830738</v>
       </c>
       <c r="E98" s="0">
@@ -21889,7 +21889,7 @@
       <c r="C99" s="0" t="n">
         <v>0.519</v>
       </c>
-      <c r="D99" t="n">
+      <c r="D99" s="0" t="n">
         <v>0.02203675732016563</v>
       </c>
       <c r="E99" s="0">
@@ -21924,7 +21924,7 @@
       <c r="C100" s="0" t="n">
         <v>0.517</v>
       </c>
-      <c r="D100" t="n">
+      <c r="D100" s="0" t="n">
         <v>0.02238716930150986</v>
       </c>
       <c r="E100" s="0">
@@ -21959,7 +21959,7 @@
       <c r="C101" s="0" t="n">
         <v>0.514</v>
       </c>
-      <c r="D101" t="n">
+      <c r="D101" s="0" t="n">
         <v>0.02200327999889851</v>
       </c>
       <c r="E101" s="0">
@@ -21994,7 +21994,7 @@
       <c r="C102" s="0" t="n">
         <v>0.512</v>
       </c>
-      <c r="D102" t="n">
+      <c r="D102" s="0" t="n">
         <v>0.02229078486561775</v>
       </c>
       <c r="E102" s="0">
@@ -22029,7 +22029,7 @@
       <c r="C103" s="0" t="n">
         <v>0.51</v>
       </c>
-      <c r="D103" t="n">
+      <c r="D103" s="0" t="n">
         <v>0.02204912714660168</v>
       </c>
       <c r="E103" s="0">
@@ -22064,7 +22064,7 @@
       <c r="C104" s="0" t="n">
         <v>0.508</v>
       </c>
-      <c r="D104" t="n">
+      <c r="D104" s="0" t="n">
         <v>0.02202761545777321</v>
       </c>
       <c r="E104" s="0">
@@ -22099,7 +22099,7 @@
       <c r="C105" s="0" t="n">
         <v>0.506</v>
       </c>
-      <c r="D105" t="n">
+      <c r="D105" s="0" t="n">
         <v>0.02176796086132526</v>
       </c>
       <c r="E105" s="0">
@@ -22134,7 +22134,7 @@
       <c r="C106" s="0" t="n">
         <v>0.503</v>
       </c>
-      <c r="D106" t="n">
+      <c r="D106" s="0" t="n">
         <v>0.02218662574887276</v>
       </c>
       <c r="E106" s="0">
@@ -22169,7 +22169,7 @@
       <c r="C107" s="0" t="n">
         <v>0.501</v>
       </c>
-      <c r="D107" t="n">
+      <c r="D107" s="0" t="n">
         <v>0.02234361320734024</v>
       </c>
       <c r="E107" s="0">
@@ -22204,7 +22204,7 @@
       <c r="C108" s="0" t="n">
         <v>0.499</v>
       </c>
-      <c r="D108" t="n">
+      <c r="D108" s="0" t="n">
         <v>0.02194085530936718</v>
       </c>
       <c r="E108" s="0">
@@ -22239,7 +22239,7 @@
       <c r="C109" s="0" t="n">
         <v>0.496</v>
       </c>
-      <c r="D109" t="n">
+      <c r="D109" s="0" t="n">
         <v>0.02266308106482029</v>
       </c>
       <c r="E109" s="0">
@@ -22274,7 +22274,7 @@
       <c r="C110" s="0" t="n">
         <v>0.494</v>
       </c>
-      <c r="D110" t="n">
+      <c r="D110" s="0" t="n">
         <v>0.02264226041734219</v>
       </c>
       <c r="E110" s="0">
@@ -22309,7 +22309,7 @@
       <c r="C111" s="0" t="n">
         <v>0.492</v>
       </c>
-      <c r="D111" t="n">
+      <c r="D111" s="0" t="n">
         <v>0.02145604602992535</v>
       </c>
       <c r="E111" s="0">
@@ -22344,7 +22344,7 @@
       <c r="C112" s="0" t="n">
         <v>0.49</v>
       </c>
-      <c r="D112" t="n">
+      <c r="D112" s="0" t="n">
         <v>0.02272169478237629</v>
       </c>
       <c r="E112" s="0">
@@ -22379,7 +22379,7 @@
       <c r="C113" s="0" t="n">
         <v>0.488</v>
       </c>
-      <c r="D113" t="n">
+      <c r="D113" s="0" t="n">
         <v>0.02283627167344093</v>
       </c>
       <c r="E113" s="0">
@@ -22414,7 +22414,7 @@
       <c r="C114" s="0" t="n">
         <v>0.485</v>
       </c>
-      <c r="D114" t="n">
+      <c r="D114" s="0" t="n">
         <v>0.02256097830832005</v>
       </c>
       <c r="E114" s="0">
@@ -22449,7 +22449,7 @@
       <c r="C115" s="0" t="n">
         <v>0.483</v>
       </c>
-      <c r="D115" t="n">
+      <c r="D115" s="0" t="n">
         <v>0.02283190004527569</v>
       </c>
       <c r="E115" s="0">
@@ -22484,7 +22484,7 @@
       <c r="C116" s="0" t="n">
         <v>0.481</v>
       </c>
-      <c r="D116" t="n">
+      <c r="D116" s="0" t="n">
         <v>0.02224512957036495</v>
       </c>
       <c r="E116" s="0">
@@ -22519,7 +22519,7 @@
       <c r="C117" s="0" t="n">
         <v>0.479</v>
       </c>
-      <c r="D117" t="n">
+      <c r="D117" s="0" t="n">
         <v>0.02277129143476486</v>
       </c>
       <c r="E117" s="0">
@@ -22554,7 +22554,7 @@
       <c r="C118" s="0" t="n">
         <v>0.477</v>
       </c>
-      <c r="D118" t="n">
+      <c r="D118" s="0" t="n">
         <v>0.02282169088721275</v>
       </c>
       <c r="E118" s="0">
@@ -22589,7 +22589,7 @@
       <c r="C119" s="0" t="n">
         <v>0.474</v>
       </c>
-      <c r="D119" t="n">
+      <c r="D119" s="0" t="n">
         <v>0.02233251929283142</v>
       </c>
       <c r="E119" s="0">
@@ -22624,7 +22624,7 @@
       <c r="C120" s="0" t="n">
         <v>0.473</v>
       </c>
-      <c r="D120" t="n">
+      <c r="D120" s="0" t="n">
         <v>0.02308384887874126</v>
       </c>
       <c r="E120" s="0">
@@ -22659,7 +22659,7 @@
       <c r="C121" s="0" t="n">
         <v>0.47</v>
       </c>
-      <c r="D121" t="n">
+      <c r="D121" s="0" t="n">
         <v>0.02248584665358067</v>
       </c>
       <c r="E121" s="0">
@@ -22694,7 +22694,7 @@
       <c r="C122" s="0" t="n">
         <v>0.468</v>
       </c>
-      <c r="D122" t="n">
+      <c r="D122" s="0" t="n">
         <v>0.02315918728709221</v>
       </c>
       <c r="E122" s="0">
@@ -22729,7 +22729,7 @@
       <c r="C123" s="0" t="n">
         <v>0.466</v>
       </c>
-      <c r="D123" t="n">
+      <c r="D123" s="0" t="n">
         <v>0.02308138087391853</v>
       </c>
       <c r="E123" s="0">
@@ -22764,7 +22764,7 @@
       <c r="C124" s="0" t="n">
         <v>0.464</v>
       </c>
-      <c r="D124" t="n">
+      <c r="D124" s="0" t="n">
         <v>0.02228741347789764</v>
       </c>
       <c r="E124" s="0">
@@ -22799,7 +22799,7 @@
       <c r="C125" s="0" t="n">
         <v>0.462</v>
       </c>
-      <c r="D125" t="n">
+      <c r="D125" s="0" t="n">
         <v>0.02303110808134079</v>
       </c>
       <c r="E125" s="0">
@@ -22834,7 +22834,7 @@
       <c r="C126" s="0" t="n">
         <v>0.46</v>
       </c>
-      <c r="D126" t="n">
+      <c r="D126" s="0" t="n">
         <v>0.02348831482231617</v>
       </c>
       <c r="E126" s="0">
@@ -22869,7 +22869,7 @@
       <c r="C127" s="0" t="n">
         <v>0.458</v>
       </c>
-      <c r="D127" t="n">
+      <c r="D127" s="0" t="n">
         <v>0.02262923307716846</v>
       </c>
       <c r="E127" s="0">
@@ -22904,7 +22904,7 @@
       <c r="C128" s="0" t="n">
         <v>0.455</v>
       </c>
-      <c r="D128" t="n">
+      <c r="D128" s="0" t="n">
         <v>0.02375646680593491</v>
       </c>
       <c r="E128" s="0">
@@ -22939,7 +22939,7 @@
       <c r="C129" s="0" t="n">
         <v>0.453</v>
       </c>
-      <c r="D129" t="n">
+      <c r="D129" s="0" t="n">
         <v>0.02298040315508842</v>
       </c>
       <c r="E129" s="0">
@@ -22974,7 +22974,7 @@
       <c r="C130" s="0" t="n">
         <v>0.451</v>
       </c>
-      <c r="D130" t="n">
+      <c r="D130" s="0" t="n">
         <v>0.0228426568210125</v>
       </c>
       <c r="E130" s="0">
@@ -23009,7 +23009,7 @@
       <c r="C131" s="0" t="n">
         <v>0.449</v>
       </c>
-      <c r="D131" t="n">
+      <c r="D131" s="0" t="n">
         <v>0.02334821410477161</v>
       </c>
       <c r="E131" s="0">
@@ -23044,7 +23044,7 @@
       <c r="C132" s="0" t="n">
         <v>0.447</v>
       </c>
-      <c r="D132" t="n">
+      <c r="D132" s="0" t="n">
         <v>0.02255835197865963</v>
       </c>
       <c r="E132" s="0">
@@ -23079,7 +23079,7 @@
       <c r="C133" s="0" t="n">
         <v>0.445</v>
       </c>
-      <c r="D133" t="n">
+      <c r="D133" s="0" t="n">
         <v>0.02312240190804005</v>
       </c>
       <c r="E133" s="0">
@@ -23114,7 +23114,7 @@
       <c r="C134" s="0" t="n">
         <v>0.443</v>
       </c>
-      <c r="D134" t="n">
+      <c r="D134" s="0" t="n">
         <v>0.02291266620159149</v>
       </c>
       <c r="E134" s="0">
@@ -23149,7 +23149,7 @@
       <c r="C135" s="0" t="n">
         <v>0.441</v>
       </c>
-      <c r="D135" t="n">
+      <c r="D135" s="0" t="n">
         <v>0.023176034912467</v>
       </c>
       <c r="E135" s="0">
@@ -23184,7 +23184,7 @@
       <c r="C136" s="0" t="n">
         <v>0.439</v>
       </c>
-      <c r="D136" t="n">
+      <c r="D136" s="0" t="n">
         <v>0.02292532101273537</v>
       </c>
       <c r="E136" s="0">
@@ -23219,7 +23219,7 @@
       <c r="C137" s="0" t="n">
         <v>0.437</v>
       </c>
-      <c r="D137" t="n">
+      <c r="D137" s="0" t="n">
         <v>0.02327945083379745</v>
       </c>
       <c r="E137" s="0">
@@ -23254,7 +23254,7 @@
       <c r="C138" s="0" t="n">
         <v>0.434</v>
       </c>
-      <c r="D138" t="n">
+      <c r="D138" s="0" t="n">
         <v>0.02313651889562607</v>
       </c>
       <c r="E138" s="0">
@@ -23289,7 +23289,7 @@
       <c r="C139" s="0" t="n">
         <v>0.432</v>
       </c>
-      <c r="D139" t="n">
+      <c r="D139" s="0" t="n">
         <v>0.02359609119594097</v>
       </c>
       <c r="E139" s="0">
@@ -23324,7 +23324,7 @@
       <c r="C140" s="0" t="n">
         <v>0.43</v>
       </c>
-      <c r="D140" t="n">
+      <c r="D140" s="0" t="n">
         <v>0.02316553890705109</v>
       </c>
       <c r="E140" s="0">
@@ -23359,7 +23359,7 @@
       <c r="C141" s="0" t="n">
         <v>0.428</v>
       </c>
-      <c r="D141" t="n">
+      <c r="D141" s="0" t="n">
         <v>0.02403800003230572</v>
       </c>
       <c r="E141" s="0">
@@ -23394,7 +23394,7 @@
       <c r="C142" s="0" t="n">
         <v>0.426</v>
       </c>
-      <c r="D142" t="n">
+      <c r="D142" s="0" t="n">
         <v>0.0228748694062233</v>
       </c>
       <c r="E142" s="0">
@@ -23429,7 +23429,7 @@
       <c r="C143" s="0" t="n">
         <v>0.424</v>
       </c>
-      <c r="D143" t="n">
+      <c r="D143" s="0" t="n">
         <v>0.02321753092110157</v>
       </c>
       <c r="E143" s="0">
@@ -23464,7 +23464,7 @@
       <c r="C144" s="0" t="n">
         <v>0.422</v>
       </c>
-      <c r="D144" t="n">
+      <c r="D144" s="0" t="n">
         <v>0.02334983088076115</v>
       </c>
       <c r="E144" s="0">
@@ -23499,7 +23499,7 @@
       <c r="C145" s="0" t="n">
         <v>0.42</v>
       </c>
-      <c r="D145" t="n">
+      <c r="D145" s="0" t="n">
         <v>0.02308961376547813</v>
       </c>
       <c r="E145" s="0">
@@ -23534,7 +23534,7 @@
       <c r="C146" s="0" t="n">
         <v>0.418</v>
       </c>
-      <c r="D146" t="n">
+      <c r="D146" s="0" t="n">
         <v>0.02444537356495857</v>
       </c>
       <c r="E146" s="0">
@@ -23569,7 +23569,7 @@
       <c r="C147" s="0" t="n">
         <v>0.416</v>
       </c>
-      <c r="D147" t="n">
+      <c r="D147" s="0" t="n">
         <v>0.02307135425508022</v>
       </c>
       <c r="E147" s="0">
@@ -23604,7 +23604,7 @@
       <c r="C148" s="0" t="n">
         <v>0.413</v>
       </c>
-      <c r="D148" t="n">
+      <c r="D148" s="0" t="n">
         <v>0.02379290014505386</v>
       </c>
       <c r="E148" s="0">
@@ -23639,7 +23639,7 @@
       <c r="C149" s="0" t="n">
         <v>0.411</v>
       </c>
-      <c r="D149" t="n">
+      <c r="D149" s="0" t="n">
         <v>0.02341685071587563</v>
       </c>
       <c r="E149" s="0">
@@ -23674,7 +23674,7 @@
       <c r="C150" s="0" t="n">
         <v>0.409</v>
       </c>
-      <c r="D150" t="n">
+      <c r="D150" s="0" t="n">
         <v>0.02343933098018169</v>
       </c>
       <c r="E150" s="0">
@@ -23709,7 +23709,7 @@
       <c r="C151" s="0" t="n">
         <v>0.407</v>
       </c>
-      <c r="D151" t="n">
+      <c r="D151" s="0" t="n">
         <v>0.02361765690147877</v>
       </c>
       <c r="E151" s="0">
@@ -23744,7 +23744,7 @@
       <c r="C152" s="0" t="n">
         <v>0.405</v>
       </c>
-      <c r="D152" t="n">
+      <c r="D152" s="0" t="n">
         <v>0.02412284165620804</v>
       </c>
       <c r="E152" s="0">
@@ -23779,7 +23779,7 @@
       <c r="C153" s="0" t="n">
         <v>0.403</v>
       </c>
-      <c r="D153" t="n">
+      <c r="D153" s="0" t="n">
         <v>0.02367998659610748</v>
       </c>
       <c r="E153" s="0">
@@ -23814,7 +23814,7 @@
       <c r="C154" s="0" t="n">
         <v>0.401</v>
       </c>
-      <c r="D154" t="n">
+      <c r="D154" s="0" t="n">
         <v>0.02378236874938011</v>
       </c>
       <c r="E154" s="0">
@@ -23849,7 +23849,7 @@
       <c r="C155" s="0" t="n">
         <v>0.399</v>
       </c>
-      <c r="D155" t="n">
+      <c r="D155" s="0" t="n">
         <v>0.02381190285086632</v>
       </c>
       <c r="E155" s="0">
@@ -23884,7 +23884,7 @@
       <c r="C156" s="0" t="n">
         <v>0.397</v>
       </c>
-      <c r="D156" t="n">
+      <c r="D156" s="0" t="n">
         <v>0.02335663884878159</v>
       </c>
       <c r="E156" s="0">
@@ -23919,7 +23919,7 @@
       <c r="C157" s="0" t="n">
         <v>0.395</v>
       </c>
-      <c r="D157" t="n">
+      <c r="D157" s="0" t="n">
         <v>0.02376625686883926</v>
       </c>
       <c r="E157" s="0">
@@ -23954,7 +23954,7 @@
       <c r="C158" s="0" t="n">
         <v>0.393</v>
       </c>
-      <c r="D158" t="n">
+      <c r="D158" s="0" t="n">
         <v>0.02348150312900543</v>
       </c>
       <c r="E158" s="0">
@@ -23989,7 +23989,7 @@
       <c r="C159" s="0" t="n">
         <v>0.39</v>
       </c>
-      <c r="D159" t="n">
+      <c r="D159" s="0" t="n">
         <v>0.02421257458627224</v>
       </c>
       <c r="E159" s="0">
@@ -24024,7 +24024,7 @@
       <c r="C160" s="0" t="n">
         <v>0.388</v>
       </c>
-      <c r="D160" t="n">
+      <c r="D160" s="0" t="n">
         <v>0.02338164113461971</v>
       </c>
       <c r="E160" s="0">
@@ -24059,7 +24059,7 @@
       <c r="C161" s="0" t="n">
         <v>0.386</v>
       </c>
-      <c r="D161" t="n">
+      <c r="D161" s="0" t="n">
         <v>0.02417968027293682</v>
       </c>
       <c r="E161" s="0">
@@ -24094,7 +24094,7 @@
       <c r="C162" s="0" t="n">
         <v>0.384</v>
       </c>
-      <c r="D162" t="n">
+      <c r="D162" s="0" t="n">
         <v>0.02359800599515438</v>
       </c>
       <c r="E162" s="0">
@@ -24129,7 +24129,7 @@
       <c r="C163" s="0" t="n">
         <v>0.382</v>
       </c>
-      <c r="D163" t="n">
+      <c r="D163" s="0" t="n">
         <v>0.02405710332095623</v>
       </c>
       <c r="E163" s="0">
@@ -24164,7 +24164,7 @@
       <c r="C164" s="0" t="n">
         <v>0.38</v>
       </c>
-      <c r="D164" t="n">
+      <c r="D164" s="0" t="n">
         <v>0.02362007275223732</v>
       </c>
       <c r="E164" s="0">
@@ -24199,7 +24199,7 @@
       <c r="C165" s="0" t="n">
         <v>0.378</v>
       </c>
-      <c r="D165" t="n">
+      <c r="D165" s="0" t="n">
         <v>0.02441132627427578</v>
       </c>
       <c r="E165" s="0">
@@ -24234,7 +24234,7 @@
       <c r="C166" s="0" t="n">
         <v>0.375</v>
       </c>
-      <c r="D166" t="n">
+      <c r="D166" s="0" t="n">
         <v>0.02377547696232796</v>
       </c>
       <c r="E166" s="0">
@@ -24269,7 +24269,7 @@
       <c r="C167" s="0" t="n">
         <v>0.373</v>
       </c>
-      <c r="D167" t="n">
+      <c r="D167" s="0" t="n">
         <v>0.02424614503979683</v>
       </c>
       <c r="E167" s="0">
@@ -24304,7 +24304,7 @@
       <c r="C168" s="0" t="n">
         <v>0.371</v>
       </c>
-      <c r="D168" t="n">
+      <c r="D168" s="0" t="n">
         <v>0.02394500561058521</v>
       </c>
       <c r="E168" s="0">
@@ -24339,7 +24339,7 @@
       <c r="C169" s="0" t="n">
         <v>0.369</v>
       </c>
-      <c r="D169" t="n">
+      <c r="D169" s="0" t="n">
         <v>0.02406875789165497</v>
       </c>
       <c r="E169" s="0">
@@ -24374,7 +24374,7 @@
       <c r="C170" s="0" t="n">
         <v>0.367</v>
       </c>
-      <c r="D170" t="n">
+      <c r="D170" s="0" t="n">
         <v>0.02440095134079456</v>
       </c>
       <c r="E170" s="0">
@@ -24409,7 +24409,7 @@
       <c r="C171" s="0" t="n">
         <v>0.365</v>
       </c>
-      <c r="D171" t="n">
+      <c r="D171" s="0" t="n">
         <v>0.02434027567505836</v>
       </c>
       <c r="E171" s="0">
@@ -24444,7 +24444,7 @@
       <c r="C172" s="0" t="n">
         <v>0.362</v>
       </c>
-      <c r="D172" t="n">
+      <c r="D172" s="0" t="n">
         <v>0.02376594208180904</v>
       </c>
       <c r="E172" s="0">
@@ -24479,7 +24479,7 @@
       <c r="C173" s="0" t="n">
         <v>0.361</v>
       </c>
-      <c r="D173" t="n">
+      <c r="D173" s="0" t="n">
         <v>0.02431243099272251</v>
       </c>
       <c r="E173" s="0">
@@ -24514,7 +24514,7 @@
       <c r="C174" s="0" t="n">
         <v>0.358</v>
       </c>
-      <c r="D174" t="n">
+      <c r="D174" s="0" t="n">
         <v>0.02424491569399834</v>
       </c>
       <c r="E174" s="0">
@@ -24549,7 +24549,7 @@
       <c r="C175" s="0" t="n">
         <v>0.356</v>
       </c>
-      <c r="D175" t="n">
+      <c r="D175" s="0" t="n">
         <v>0.02432944253087044</v>
       </c>
       <c r="E175" s="0">
@@ -24584,7 +24584,7 @@
       <c r="C176" s="0" t="n">
         <v>0.354</v>
       </c>
-      <c r="D176" t="n">
+      <c r="D176" s="0" t="n">
         <v>0.02473657205700874</v>
       </c>
       <c r="E176" s="0">
@@ -24619,7 +24619,7 @@
       <c r="C177" s="0" t="n">
         <v>0.352</v>
       </c>
-      <c r="D177" t="n">
+      <c r="D177" s="0" t="n">
         <v>0.02427547425031662</v>
       </c>
       <c r="E177" s="0">
@@ -24654,7 +24654,7 @@
       <c r="C178" s="0" t="n">
         <v>0.35</v>
       </c>
-      <c r="D178" t="n">
+      <c r="D178" s="0" t="n">
         <v>0.02418882772326469</v>
       </c>
       <c r="E178" s="0">
@@ -24689,7 +24689,7 @@
       <c r="C179" s="0" t="n">
         <v>0.348</v>
       </c>
-      <c r="D179" t="n">
+      <c r="D179" s="0" t="n">
         <v>0.0245915874838829</v>
       </c>
       <c r="E179" s="0">
@@ -24724,7 +24724,7 @@
       <c r="C180" s="0" t="n">
         <v>0.346</v>
       </c>
-      <c r="D180" t="n">
+      <c r="D180" s="0" t="n">
         <v>0.02487228251993656</v>
       </c>
       <c r="E180" s="0">
@@ -24759,7 +24759,7 @@
       <c r="C181" s="0" t="n">
         <v>0.343</v>
       </c>
-      <c r="D181" t="n">
+      <c r="D181" s="0" t="n">
         <v>0.02499474212527275</v>
       </c>
       <c r="E181" s="0">
@@ -24794,7 +24794,7 @@
       <c r="C182" s="0" t="n">
         <v>0.341</v>
       </c>
-      <c r="D182" t="n">
+      <c r="D182" s="0" t="n">
         <v>0.02505173347890377</v>
       </c>
       <c r="E182" s="0">
@@ -24829,7 +24829,7 @@
       <c r="C183" s="0" t="n">
         <v>0.339</v>
       </c>
-      <c r="D183" t="n">
+      <c r="D183" s="0" t="n">
         <v>0.02456580474972725</v>
       </c>
       <c r="E183" s="0">
@@ -24864,7 +24864,7 @@
       <c r="C184" s="0" t="n">
         <v>0.337</v>
       </c>
-      <c r="D184" t="n">
+      <c r="D184" s="0" t="n">
         <v>0.02429625019431114</v>
       </c>
       <c r="E184" s="0">
@@ -24899,7 +24899,7 @@
       <c r="C185" s="0" t="n">
         <v>0.335</v>
       </c>
-      <c r="D185" t="n">
+      <c r="D185" s="0" t="n">
         <v>0.02401648834347725</v>
       </c>
       <c r="E185" s="0">
@@ -24934,7 +24934,7 @@
       <c r="C186" s="0" t="n">
         <v>0.333</v>
       </c>
-      <c r="D186" t="n">
+      <c r="D186" s="0" t="n">
         <v>0.0249500460922718</v>
       </c>
       <c r="E186" s="0">
@@ -24969,7 +24969,7 @@
       <c r="C187" s="0" t="n">
         <v>0.33</v>
       </c>
-      <c r="D187" t="n">
+      <c r="D187" s="0" t="n">
         <v>0.02474693581461906</v>
       </c>
       <c r="E187" s="0">
@@ -25004,7 +25004,7 @@
       <c r="C188" s="0" t="n">
         <v>0.328</v>
       </c>
-      <c r="D188" t="n">
+      <c r="D188" s="0" t="n">
         <v>0.0247977115213871</v>
       </c>
       <c r="E188" s="0">
@@ -25039,7 +25039,7 @@
       <c r="C189" s="0" t="n">
         <v>0.327</v>
       </c>
-      <c r="D189" t="n">
+      <c r="D189" s="0" t="n">
         <v>0.02455391362309456</v>
       </c>
       <c r="E189" s="0">
@@ -25074,7 +25074,7 @@
       <c r="C190" s="0" t="n">
         <v>0.324</v>
       </c>
-      <c r="D190" t="n">
+      <c r="D190" s="0" t="n">
         <v>0.02486999705433846</v>
       </c>
       <c r="E190" s="0">
@@ -25109,7 +25109,7 @@
       <c r="C191" s="0" t="n">
         <v>0.322</v>
       </c>
-      <c r="D191" t="n">
+      <c r="D191" s="0" t="n">
         <v>0.02434824593365192</v>
       </c>
       <c r="E191" s="0">
@@ -25144,7 +25144,7 @@
       <c r="C192" s="0" t="n">
         <v>0.32</v>
       </c>
-      <c r="D192" t="n">
+      <c r="D192" s="0" t="n">
         <v>0.02544496022164822</v>
       </c>
       <c r="E192" s="0">
@@ -25179,7 +25179,7 @@
       <c r="C193" s="0" t="n">
         <v>0.317</v>
       </c>
-      <c r="D193" t="n">
+      <c r="D193" s="0" t="n">
         <v>0.02464304119348526</v>
       </c>
       <c r="E193" s="0">
@@ -25214,7 +25214,7 @@
       <c r="C194" s="0" t="n">
         <v>0.315</v>
       </c>
-      <c r="D194" t="n">
+      <c r="D194" s="0" t="n">
         <v>0.02476061508059502</v>
       </c>
       <c r="E194" s="0">
@@ -25249,7 +25249,7 @@
       <c r="C195" s="0" t="n">
         <v>0.313</v>
       </c>
-      <c r="D195" t="n">
+      <c r="D195" s="0" t="n">
         <v>0.02476061508059502</v>
       </c>
       <c r="E195" s="0">
@@ -25284,7 +25284,7 @@
       <c r="C196" s="0" t="n">
         <v>0.311</v>
       </c>
-      <c r="D196" t="n">
+      <c r="D196" s="0" t="n">
         <v>0.024</v>
       </c>
       <c r="E196" s="0">
@@ -25318,7 +25318,7 @@
       <c r="C197" s="0" t="n">
         <v>0.309</v>
       </c>
-      <c r="D197" t="n">
+      <c r="D197" s="0" t="n">
         <v>0.024</v>
       </c>
       <c r="E197" s="0">
@@ -25352,7 +25352,7 @@
       <c r="C198" s="0" t="n">
         <v>0.306</v>
       </c>
-      <c r="D198" t="n">
+      <c r="D198" s="0" t="n">
         <v>0.024</v>
       </c>
       <c r="E198" s="0">
@@ -25386,7 +25386,7 @@
       <c r="C199" s="0" t="n">
         <v>0.304</v>
       </c>
-      <c r="D199" t="n">
+      <c r="D199" s="0" t="n">
         <v>0.024</v>
       </c>
       <c r="E199" s="0">
@@ -25420,7 +25420,7 @@
       <c r="C200" s="0" t="n">
         <v>0.301</v>
       </c>
-      <c r="D200" t="n">
+      <c r="D200" s="0" t="n">
         <v>0.024</v>
       </c>
       <c r="E200" s="0">
@@ -25454,7 +25454,7 @@
       <c r="C201" s="0" t="n">
         <v>0.299</v>
       </c>
-      <c r="D201" t="n">
+      <c r="D201" s="0" t="n">
         <v>0.024</v>
       </c>
       <c r="E201" s="0">
@@ -25488,7 +25488,7 @@
       <c r="C202" s="0" t="n">
         <v>0.297</v>
       </c>
-      <c r="D202" t="n">
+      <c r="D202" s="0" t="n">
         <v>0.024</v>
       </c>
       <c r="E202" s="0">
@@ -25522,7 +25522,7 @@
       <c r="C203" s="0" t="n">
         <v>0.295</v>
       </c>
-      <c r="D203" t="n">
+      <c r="D203" s="0" t="n">
         <v>0.024</v>
       </c>
       <c r="E203" s="0">
@@ -25556,7 +25556,7 @@
       <c r="C204" s="0" t="n">
         <v>0.293</v>
       </c>
-      <c r="D204" t="n">
+      <c r="D204" s="0" t="n">
         <v>0.024</v>
       </c>
       <c r="E204" s="0">
@@ -25590,7 +25590,7 @@
       <c r="C205" s="0" t="n">
         <v>0.291</v>
       </c>
-      <c r="D205" t="n">
+      <c r="D205" s="0" t="n">
         <v>0.024</v>
       </c>
       <c r="E205" s="0">
@@ -25624,7 +25624,7 @@
       <c r="C206" s="0" t="n">
         <v>0.288</v>
       </c>
-      <c r="D206" t="n">
+      <c r="D206" s="0" t="n">
         <v>0.024</v>
       </c>
       <c r="E206" s="0">
@@ -25658,7 +25658,7 @@
       <c r="C207" s="0" t="n">
         <v>0.286</v>
       </c>
-      <c r="D207" t="n">
+      <c r="D207" s="0" t="n">
         <v>0.024</v>
       </c>
       <c r="E207" s="0">
@@ -25692,7 +25692,7 @@
       <c r="C208" s="0" t="n">
         <v>0.284</v>
       </c>
-      <c r="D208" t="n">
+      <c r="D208" s="0" t="n">
         <v>0.024</v>
       </c>
       <c r="E208" s="0">
@@ -25726,7 +25726,7 @@
       <c r="C209" s="0" t="n">
         <v>0.282</v>
       </c>
-      <c r="D209" t="n">
+      <c r="D209" s="0" t="n">
         <v>0.024</v>
       </c>
       <c r="E209" s="0">
@@ -25760,7 +25760,7 @@
       <c r="C210" s="0" t="n">
         <v>0.279</v>
       </c>
-      <c r="D210" t="n">
+      <c r="D210" s="0" t="n">
         <v>0.024</v>
       </c>
       <c r="E210" s="0">
@@ -25794,7 +25794,7 @@
       <c r="C211" s="0" t="n">
         <v>0.277</v>
       </c>
-      <c r="D211" t="n">
+      <c r="D211" s="0" t="n">
         <v>0.024</v>
       </c>
       <c r="E211" s="0">
@@ -25828,7 +25828,7 @@
       <c r="C212" s="0" t="n">
         <v>0.275</v>
       </c>
-      <c r="D212" t="n">
+      <c r="D212" s="0" t="n">
         <v>0.024</v>
       </c>
       <c r="E212" s="0">
@@ -25862,7 +25862,7 @@
       <c r="C213" s="0" t="n">
         <v>0.272</v>
       </c>
-      <c r="D213" t="n">
+      <c r="D213" s="0" t="n">
         <v>0.024</v>
       </c>
       <c r="E213" s="0">
@@ -25896,7 +25896,7 @@
       <c r="C214" s="0" t="n">
         <v>0.27</v>
       </c>
-      <c r="D214" t="n">
+      <c r="D214" s="0" t="n">
         <v>0.024</v>
       </c>
       <c r="E214" s="0">
@@ -25930,7 +25930,7 @@
       <c r="C215" s="0" t="n">
         <v>0.268</v>
       </c>
-      <c r="D215" t="n">
+      <c r="D215" s="0" t="n">
         <v>0.024</v>
       </c>
       <c r="E215" s="0">
@@ -25964,7 +25964,7 @@
       <c r="C216" s="0" t="n">
         <v>0.265</v>
       </c>
-      <c r="D216" t="n">
+      <c r="D216" s="0" t="n">
         <v>0.024</v>
       </c>
       <c r="E216" s="0">
@@ -25998,7 +25998,7 @@
       <c r="C217" s="0" t="n">
         <v>0.263</v>
       </c>
-      <c r="D217" t="n">
+      <c r="D217" s="0" t="n">
         <v>0.024</v>
       </c>
       <c r="E217" s="0">
@@ -26032,7 +26032,7 @@
       <c r="C218" s="0" t="n">
         <v>0.261</v>
       </c>
-      <c r="D218" t="n">
+      <c r="D218" s="0" t="n">
         <v>0.024</v>
       </c>
       <c r="E218" s="0">
@@ -26066,7 +26066,7 @@
       <c r="C219" s="0" t="n">
         <v>0.259</v>
       </c>
-      <c r="D219" t="n">
+      <c r="D219" s="0" t="n">
         <v>0.024</v>
       </c>
       <c r="E219" s="0">
@@ -26100,7 +26100,7 @@
       <c r="C220" s="0" t="n">
         <v>0.256</v>
       </c>
-      <c r="D220" t="n">
+      <c r="D220" s="0" t="n">
         <v>0.024</v>
       </c>
       <c r="E220" s="0">
@@ -26134,7 +26134,7 @@
       <c r="C221" s="0" t="n">
         <v>0.254</v>
       </c>
-      <c r="D221" t="n">
+      <c r="D221" s="0" t="n">
         <v>0.024</v>
       </c>
       <c r="E221" s="0">
@@ -26168,7 +26168,7 @@
       <c r="C222" s="0" t="n">
         <v>0.252</v>
       </c>
-      <c r="D222" t="n">
+      <c r="D222" s="0" t="n">
         <v>0.024</v>
       </c>
       <c r="E222" s="0">
@@ -26202,7 +26202,7 @@
       <c r="C223" s="0" t="n">
         <v>0.252</v>
       </c>
-      <c r="D223" t="n">
+      <c r="D223" s="0" t="n">
         <v>0.024</v>
       </c>
       <c r="E223" s="0">
